--- a/docs/xlsx/jobs-2026-09-03.xlsx
+++ b/docs/xlsx/jobs-2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="494">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,1471 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Camp Cabin Leader (Part Time)</t>
+  </si>
+  <si>
+    <t>Los Angeles Unified School District</t>
+  </si>
+  <si>
+    <t>Los Angeles, CA</t>
+  </si>
+  <si>
+    <t>Permanent</t>
+  </si>
+  <si>
+    <t>$26.40 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education-outdoor-recreation</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-camp-cabin-leader-part-time-los-angeles-california/3454614240</t>
+  </si>
+  <si>
+    <t>Conservation Grazing Program Manager</t>
+  </si>
+  <si>
+    <t>Midpeninsula Regional Open Space District</t>
+  </si>
+  <si>
+    <t>Los Altos, CA, CA</t>
+  </si>
+  <si>
+    <t>$133,233 - $166,419 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-conservation-grazing-program-manager-los-altos-ca-california/4687717106</t>
+  </si>
+  <si>
+    <t>Crew Leader</t>
+  </si>
+  <si>
+    <t>Earth Conservation Corps</t>
+  </si>
+  <si>
+    <t>Washington, DC</t>
+  </si>
+  <si>
+    <t>$50,000 - $55,000 per year</t>
+  </si>
+  <si>
+    <t>environmental-education-forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-crew-leader-washington-dc/4502673065</t>
+  </si>
+  <si>
+    <t>Development and Communications Manager</t>
+  </si>
+  <si>
+    <t>Evergreen Audubon &amp; Nature Center</t>
+  </si>
+  <si>
+    <t>Evergreen, CO</t>
+  </si>
+  <si>
+    <t>$21 - $25 per hour</t>
+  </si>
+  <si>
+    <t>admin-leadership</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-development-and-communications-manager-evergreen-colorado/5802896989</t>
+  </si>
+  <si>
+    <t>Eastern Washington Fish Science Manager - WMS Band 2 - Permanent - 2026-07260</t>
+  </si>
+  <si>
+    <t>Washington Department of Fish and Wildlife</t>
+  </si>
+  <si>
+    <t>Wenatchee, WA</t>
+  </si>
+  <si>
+    <t>$115,000 - $126,000 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-eastern-washington-fish-science-manager---wms-band-2---permanent---2026-07260-wenatchee-washington/5819052170</t>
+  </si>
+  <si>
+    <t>Entry-Level Field Biologist (Las Vegas, NV)</t>
+  </si>
+  <si>
+    <t>BEC Environmental, Inc.</t>
+  </si>
+  <si>
+    <t>Las Vegas, NV</t>
+  </si>
+  <si>
+    <t>$21.54 per hour</t>
+  </si>
+  <si>
+    <t>botany-ecology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-entry-level-field-biologist-las-vegas-nv-las-vegas-nevada/8357136259</t>
+  </si>
+  <si>
+    <t>Environmental &amp; Natural Resources Director</t>
+  </si>
+  <si>
+    <t>Pueblo of Laguna</t>
+  </si>
+  <si>
+    <t>Laguna, NM</t>
+  </si>
+  <si>
+    <t>$82,018 - $123,027 per year</t>
+  </si>
+  <si>
+    <t>admin-leadership-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental--natural-resources-director-laguna-new-mexico/4311973119</t>
+  </si>
+  <si>
+    <t>Environmental Analyst</t>
+  </si>
+  <si>
+    <t>NEIWPCC</t>
+  </si>
+  <si>
+    <t>Grand Isle, VT</t>
+  </si>
+  <si>
+    <t>$55,000 - $65,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-analyst-grand-isle-vermont/6737589682</t>
+  </si>
+  <si>
+    <t>Environmental Analyst – Lead Testing in Schools</t>
+  </si>
+  <si>
+    <t>Providence, RI</t>
+  </si>
+  <si>
+    <t>$65,000 - $80,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-analyst--lead-testing-in-schools-providence-rhode-island/2975811396</t>
+  </si>
+  <si>
+    <t>Environmental Education Assistant Coordinator</t>
+  </si>
+  <si>
+    <t>Kendall County Forest Preserve District</t>
+  </si>
+  <si>
+    <t>Yorkville, IL</t>
+  </si>
+  <si>
+    <t>$17 - $19 per hour</t>
+  </si>
+  <si>
+    <t>environmental-education</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-environmental-education-assistant-coordinator-yorkville-illinois/2364843252</t>
+  </si>
+  <si>
+    <t>Field Organizer</t>
+  </si>
+  <si>
+    <t>Eugene Clean Energy Fund</t>
+  </si>
+  <si>
+    <t>Eugene, OR</t>
+  </si>
+  <si>
+    <t>Temporary</t>
+  </si>
+  <si>
+    <t>$4,000 per month</t>
+  </si>
+  <si>
+    <t>admin-leadership-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-field-organizer-eugene-oregon/9604892551</t>
+  </si>
+  <si>
+    <t>Fire &amp; Landscape Ecologist</t>
+  </si>
+  <si>
+    <t>California Coastal Commission</t>
+  </si>
+  <si>
+    <t>San Francisco, CA</t>
+  </si>
+  <si>
+    <t>$4,418 - $10,732 per month</t>
+  </si>
+  <si>
+    <t>botany-ecology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fire--landscape-ecologist-san-francisco-california/7504721966</t>
+  </si>
+  <si>
+    <t>Fish Hatchery Technician</t>
+  </si>
+  <si>
+    <t>Northern Southeast Regional Aquaculture Association</t>
+  </si>
+  <si>
+    <t>Sitka, AK</t>
+  </si>
+  <si>
+    <t>$17 - $21 per hour</t>
+  </si>
+  <si>
+    <t>fisheries</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fish-hatchery-technician-sitka-alaska/7175151454</t>
+  </si>
+  <si>
+    <t>Fisheries Technician 1- Mendocino Monitoring Programs</t>
+  </si>
+  <si>
+    <t>Pacific States Marine Fisheries Commission</t>
+  </si>
+  <si>
+    <t>Fort Bragg, CA</t>
+  </si>
+  <si>
+    <t>$15.59 - $25.46 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-fisheries-technician-1--mendocino-monitoring-programs-fort-bragg-california/2536281253</t>
+  </si>
+  <si>
+    <t>Grounds and Natural Resources Division Manager</t>
+  </si>
+  <si>
+    <t>$55,000 - $58,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-grounds-and-natural-resources-division-manager-yorkville-illinois/4165608973</t>
+  </si>
+  <si>
+    <t>Hōlanikū (Kure Atoll) Restoration Volunteer</t>
+  </si>
+  <si>
+    <t>Kure Atoll Conservancy</t>
+  </si>
+  <si>
+    <t>Honolulu, HI</t>
+  </si>
+  <si>
+    <t>Unpaid</t>
+  </si>
+  <si>
+    <t>Volunteer Opportunity</t>
+  </si>
+  <si>
+    <t>restoration-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hlanik-kure-atoll-restoration-volunteer-honolulu-hawaii/8044793216</t>
+  </si>
+  <si>
+    <t>Hospital Technician I or II</t>
+  </si>
+  <si>
+    <t>Georgia Sea Turtle Center</t>
+  </si>
+  <si>
+    <t>Jekyll Island, GA</t>
+  </si>
+  <si>
+    <t>$18.75 - $21.25 per hour</t>
+  </si>
+  <si>
+    <t>marine-biology-wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-hospital-technician-i-or-ii-jekyll-island-georgia/7607637920</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>Hearty Roots</t>
+  </si>
+  <si>
+    <t>Damariscotta, ME</t>
+  </si>
+  <si>
+    <t>$19 - $22 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-instructor-damariscotta-maine/8517845255</t>
+  </si>
+  <si>
+    <t>Instrument Technician - Water Bureau</t>
+  </si>
+  <si>
+    <t>City of Portland</t>
+  </si>
+  <si>
+    <t>Portland, OR</t>
+  </si>
+  <si>
+    <t>$52.09 - $56.26 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-instrument-technician---water-bureau-portland-oregon/5519284404</t>
+  </si>
+  <si>
+    <t>Natural Resources Budget &amp; Business Assist. Manager</t>
+  </si>
+  <si>
+    <t>Washington State Department of Natural Resources</t>
+  </si>
+  <si>
+    <t>Olympia, WA</t>
+  </si>
+  <si>
+    <t>$102,888 - $119,976 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-natural-resources-budget--business-assist-manager-olympia-washington/3848293478</t>
+  </si>
+  <si>
+    <t>Program Manager</t>
+  </si>
+  <si>
+    <t>Deschutes River Conservancy</t>
+  </si>
+  <si>
+    <t>Bend, OR</t>
+  </si>
+  <si>
+    <t>$72,000 - $85,000 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-hydrology-land-trust</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-program-manager-bend-oregon/1994548902</t>
+  </si>
+  <si>
+    <t>Regulatory Compliance Specialist</t>
+  </si>
+  <si>
+    <t>VESTRA Resources, Inc.</t>
+  </si>
+  <si>
+    <t>Redding, CA</t>
+  </si>
+  <si>
+    <t>$66,560 - $90,000 per year</t>
+  </si>
+  <si>
+    <t>hydrology-policy-and-law</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-regulatory-compliance-specialist-redding-california/1408986546</t>
+  </si>
+  <si>
+    <t>Responsible Development Associate</t>
+  </si>
+  <si>
+    <t>ReImagine Appalachia</t>
+  </si>
+  <si>
+    <t>Johnstown, Remote</t>
+  </si>
+  <si>
+    <t>Achieving monthly project deliverables not to exceed a billing for 120 hours per month at a rate between $25.00-$40.00/hour</t>
+  </si>
+  <si>
+    <t>policy-and-law-sustainability</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-responsible-development-associate-johnstown-remote/1151762593</t>
+  </si>
+  <si>
+    <t>Restoration Coordinator</t>
+  </si>
+  <si>
+    <t>Kent Conservation District</t>
+  </si>
+  <si>
+    <t>Dover, DE</t>
+  </si>
+  <si>
+    <t>$65,546.05 per year</t>
+  </si>
+  <si>
+    <t>general-stewardship-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-restoration-coordinator-dover-delaware/3427698066</t>
+  </si>
+  <si>
+    <t>Science Education Coordinator</t>
+  </si>
+  <si>
+    <t>ASU Bermuda Institute of Ocean Sciences</t>
+  </si>
+  <si>
+    <t>Bermuda, Other</t>
+  </si>
+  <si>
+    <t>To be determined</t>
+  </si>
+  <si>
+    <t>environmental-education-marine-biology</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-science-education-coordinator-bermuda-other/5976123255</t>
+  </si>
+  <si>
+    <t>Senior Director, Leadership Giving</t>
+  </si>
+  <si>
+    <t>National Audubon Society</t>
+  </si>
+  <si>
+    <t>Oakland, CA</t>
+  </si>
+  <si>
+    <t>$186,000 - $208,000 per year</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-senior-director-leadership-giving-oakland-california/2479895620</t>
+  </si>
+  <si>
+    <t>TWDB - 26-120 Groundwater Scientist (Hydrologist II)</t>
+  </si>
+  <si>
+    <t>Texas Water Development Board</t>
+  </si>
+  <si>
+    <t>Austin, TX</t>
+  </si>
+  <si>
+    <t>$5,200 - $5,888 per month</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-twdb---26-120-groundwater-scientist-hydrologist-ii-austin-texas/6258910660</t>
+  </si>
+  <si>
+    <t>US Habitat Restoration Project Manager (full time)</t>
+  </si>
+  <si>
+    <t>Atlantic Salmon Federation</t>
+  </si>
+  <si>
+    <t>Brunswick, ME</t>
+  </si>
+  <si>
+    <t>$64,400 - $96,600 per year</t>
+  </si>
+  <si>
+    <t>fisheries-hydrology-restoration-general-stewardship</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-us-habitat-restoration-project-manager-full-time-brunswick-maine/4812794467</t>
+  </si>
+  <si>
+    <t>Watershed Specialist Exempt Limited Duration</t>
+  </si>
+  <si>
+    <t>City of Oakland</t>
+  </si>
+  <si>
+    <t>$54.45 - $66.85 per hour</t>
+  </si>
+  <si>
+    <t>hydrology-restoration</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-watershed-specialist-exempt-limited-duration-oakland-california/9905919440</t>
+  </si>
+  <si>
+    <t>Wildland Fire Management Supervisor</t>
+  </si>
+  <si>
+    <t>Belfair, WA</t>
+  </si>
+  <si>
+    <t>$45,924 - $67,704 per year</t>
+  </si>
+  <si>
+    <t>forestry</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildland-fire-management-supervisor-belfair-washington/6847719073</t>
+  </si>
+  <si>
+    <t>Wildlife Rehabilitation Intern</t>
+  </si>
+  <si>
+    <t>Think Wild</t>
+  </si>
+  <si>
+    <t>$1000 living expenses stipend</t>
+  </si>
+  <si>
+    <t>wildlife</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-wildlife-rehabilitation-intern-bend-oregon/4872632740</t>
+  </si>
+  <si>
+    <t>Work Planner</t>
+  </si>
+  <si>
+    <t>ArborMetrics</t>
+  </si>
+  <si>
+    <t>Traverse City, MI</t>
+  </si>
+  <si>
+    <t>$23 - $26 per hour</t>
+  </si>
+  <si>
+    <t>https://www.conservationjobboard.com/job-listing-work-planner-traverse-city-michigan/2551598509</t>
+  </si>
+  <si>
+    <t>Academic Teacher</t>
+  </si>
+  <si>
+    <t>SEEDS - Access Changes Everything</t>
+  </si>
+  <si>
+    <t>Livingston, New Jersey</t>
+  </si>
+  <si>
+    <t>Part Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 225.00 - 225.00/day</t>
+  </si>
+  <si>
+    <t>Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b94edb33f6044fb8b38114d53dba642-academic-teacher-seeds-access-changes-everything-livingston</t>
+  </si>
+  <si>
+    <t>Advocate - Education</t>
+  </si>
+  <si>
+    <t>Disability Rights Michigan</t>
+  </si>
+  <si>
+    <t>LANSING, MI</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 58000.00 - 62000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1d12acaec2eb44abb6d73eb4565f5e3c-advocate-education-disability-rights-michigan-lansing</t>
+  </si>
+  <si>
+    <t>Associate Counsel</t>
+  </si>
+  <si>
+    <t>The Wright Center for Community Health and Graduate Medical Education</t>
+  </si>
+  <si>
+    <t>Scranton, Pennsylvania</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6f0e03181a5b443fb5440250d38a4220-associate-counsel-the-wright-center-for-community-health-and-graduate-medical-education-scranton</t>
+  </si>
+  <si>
+    <t>Associate Vice President of Marketing &amp; Communications</t>
+  </si>
+  <si>
+    <t>Levine Music</t>
+  </si>
+  <si>
+    <t>Washington, District of Columbia</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Children Youth, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/39c8dabe28a747e9b441a84d478a730e-associate-vice-president-of-marketing-communications-levine-music-washington</t>
+  </si>
+  <si>
+    <t>Bookkeeper</t>
+  </si>
+  <si>
+    <t>Dawn's Place</t>
+  </si>
+  <si>
+    <t>Philadelphia, Pennsylvania</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/985b2ea0eef74b488767d9c3924d8d83-bookkeeper-dawns-place-philadelphia</t>
+  </si>
+  <si>
+    <t>Borough Instructional Manager</t>
+  </si>
+  <si>
+    <t>Literacy Inc. (LINC)</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 60000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d902b8cce3044c669eee6e3acd431ec7-borough-instructional-manager-literacy-inc-linc-new-york</t>
+  </si>
+  <si>
+    <t>California Organizing Manager</t>
+  </si>
+  <si>
+    <t>Mothers Against Media Addiction (MAMA)</t>
+  </si>
+  <si>
+    <t>Remote (California)</t>
+  </si>
+  <si>
+    <t>Full Time, Temporary</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Consumer Protection, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b388fafdd92746a4a392c2fe49d087de-california-organizing-manager-mothers-against-media-addiction-mama-new-york</t>
+  </si>
+  <si>
+    <t>Campus Coordinator, West Falls Church, VA</t>
+  </si>
+  <si>
+    <t>Falls Church, Virginia</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 43000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/20a6dd8c2e19456a8a3029147b41c0bc-campus-coordinator-west-falls-church-va-levine-music-falls-church</t>
+  </si>
+  <si>
+    <t>Career Coach (WIOA)</t>
+  </si>
+  <si>
+    <t>SER Metro-Detroit</t>
+  </si>
+  <si>
+    <t>Detroit, Michigan</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/caeae787770f4fa68f2cc7a7d086c1b1-career-coach-wioa-ser-metro-detroit-detroit</t>
+  </si>
+  <si>
+    <t>Castlemont Community Initiatives Senior Manager</t>
+  </si>
+  <si>
+    <t>Oakland Kids First</t>
+  </si>
+  <si>
+    <t>Oakland, California</t>
+  </si>
+  <si>
+    <t>USD 92000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c66d9975737d480a9c40e6f3de6b586a-castlemont-community-initiatives-senior-manager-oakland-kids-first-oakland</t>
+  </si>
+  <si>
+    <t>Chief Financial Officer - Lyons, Nebraska</t>
+  </si>
+  <si>
+    <t>Center for Rural Affairs</t>
+  </si>
+  <si>
+    <t>Lyons, Nebraska</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 138000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Community Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6b073c8dab124f88b2756a90df4431e4-chief-financial-officer-lyons-nebraska-center-for-rural-affairs-lyons</t>
+  </si>
+  <si>
+    <t>Chief Operating Officer</t>
+  </si>
+  <si>
+    <t>Daniel Murphy Scholarship Fund</t>
+  </si>
+  <si>
+    <t>Chicago, Illinois</t>
+  </si>
+  <si>
+    <t>USD 165000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b96cb37054e047229c92e521901c8d1c-chief-operating-officer-daniel-murphy-scholarship-fund-chicago</t>
+  </si>
+  <si>
+    <t>Client Advocate Specialist - Hotlines</t>
+  </si>
+  <si>
+    <t>Safe Horizon</t>
+  </si>
+  <si>
+    <t>Brooklyn, New York</t>
+  </si>
+  <si>
+    <t>USD 23.36 - 25.30/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Communications Access, Conflict Resolution</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29af03a16c5f4b96b419713fc51be58d-client-advocate-specialist-hotlines-safe-horizon-brooklyn</t>
+  </si>
+  <si>
+    <t>Clinical Partner Intimate Partner Violence (IPV)</t>
+  </si>
+  <si>
+    <t>Staten Island, New York</t>
+  </si>
+  <si>
+    <t>USD 65200.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Conflict Resolution, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5407c93603cd48c490a479ef80054df3-clinical-partner-intimate-partner-violence-ipv-safe-horizon-staten-island</t>
+  </si>
+  <si>
+    <t>Coordinador de Pequeños Animales en el Santuario Ambue Ari - Trabaja con Fauna Rescatada en la Selva Boliviana</t>
+  </si>
+  <si>
+    <t>Comunidad Inti Wara Yassi (CIWY)</t>
+  </si>
+  <si>
+    <t>Ascensión de Guarayos, Santa Cruz, BO</t>
+  </si>
+  <si>
+    <t>USD 200.00 - 200.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6abf37dee8543daa2ea296c2c3d6e3c-coordinador-de-pequenos-animales-en-el-santuario-ambue-ari-trabaja-con-fauna-rescatada-en-la-selva-boliviana-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
+  </si>
+  <si>
+    <t>Development Associate</t>
+  </si>
+  <si>
+    <t>Arts For All, Inc. NYC</t>
+  </si>
+  <si>
+    <t>USD 23.00 - 23.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/764b3b5090fd4d9b8d86df9b95ad52f6-development-associate-arts-for-all-inc-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Development Coordinator</t>
+  </si>
+  <si>
+    <t>SpeakUp!</t>
+  </si>
+  <si>
+    <t>Devon, Pennsylvania</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 68000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2941e61576404ca785e9fdf692366432-development-coordinator-speakup-devon</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT DIRECTOR &amp; GRANT WRITER</t>
+  </si>
+  <si>
+    <t>We All Really Matter Inc.</t>
+  </si>
+  <si>
+    <t>USD 125000.00 - 125000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a15f85d236574572b49be40ba248006e-development-director-grant-writer-we-all-really-matter-inc-new-york</t>
+  </si>
+  <si>
+    <t>Director of Development</t>
+  </si>
+  <si>
+    <t>The Salvation Army of Broward County</t>
+  </si>
+  <si>
+    <t>Fort Lauderdale, Florida</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 93000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Hunger Food Security, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9678fc4ee0e14b08a61188a3985e31de-director-of-development-the-salvation-army-of-broward-county-fort-lauderdale</t>
+  </si>
+  <si>
+    <t>Director of Family and Community Programs</t>
+  </si>
+  <si>
+    <t>Family Nurturing Center of MA</t>
+  </si>
+  <si>
+    <t>Dorchester, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 106000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Volunteering</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7e96be8c09ff4501b7b90431f0a0d04f-director-of-family-and-community-programs-family-nurturing-center-of-ma-dorchester</t>
+  </si>
+  <si>
+    <t>Director of Financial and Administration</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>USD 42.00 - 44.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/1a14f8bdf5f84a2699f22cc2304020c0-director-of-financial-and-administration-careers-in-nonprofits-inc-chicago</t>
+  </si>
+  <si>
+    <t>Director of Operations</t>
+  </si>
+  <si>
+    <t>Thrive for Longevity</t>
+  </si>
+  <si>
+    <t>West Palm Beach, Florida</t>
+  </si>
+  <si>
+    <t>USD 80000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Financial Literacy Personal Finance, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c19583c68f9f4fd4abd8b197fc30cefb-director-of-operations-thrive-for-longevity-west-palm-beach</t>
+  </si>
+  <si>
+    <t>Director of Parenting Education and Training</t>
+  </si>
+  <si>
+    <t>USD 98000.00 - 103000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/271e56b4b017445cb8d12f1faca4afd0-director-of-parenting-education-and-training-family-nurturing-center-of-ma-dorchester</t>
+  </si>
+  <si>
+    <t>Educational Consultant – Remote (Commission-based)</t>
+  </si>
+  <si>
+    <t>Shiva's Tutorial</t>
+  </si>
+  <si>
+    <t>Remote (IN)</t>
+  </si>
+  <si>
+    <t>Contract</t>
+  </si>
+  <si>
+    <t>INR 0.00 - 0.00/year</t>
+  </si>
+  <si>
+    <t>Education, Community Development, Economic Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3b046c85c40d49b0b5a7804b8383964a-educational-consultant-remote-commission-based-shivas-tutorial-hyderabad</t>
+  </si>
+  <si>
+    <t>Environmental Educator - KIDS for the BAY</t>
+  </si>
+  <si>
+    <t>KIDS for the BAY</t>
+  </si>
+  <si>
+    <t>Berkeley, California</t>
+  </si>
+  <si>
+    <t>USD 3840.00 - 3840.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a2ee94234ef4963af93decf4a1f22a2-environmental-educator-kids-for-the-bay-kids-for-the-bay-berkeley</t>
+  </si>
+  <si>
+    <t>Executive Director</t>
+  </si>
+  <si>
+    <t>Maynard House</t>
+  </si>
+  <si>
+    <t>Hanover, New Hampshire</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 90000.00/year</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0a534848dc9d41da90ff15a45d51b614-executive-director-maynard-house-hanover</t>
+  </si>
+  <si>
+    <t>Expert season Fundraiser</t>
+  </si>
+  <si>
+    <t>Swift Sports Organisation</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 50.00 - 100.00/month</t>
+  </si>
+  <si>
+    <t>Children Youth, Poverty, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e85c1498a8f54a568cb986ea2198e464-expert-season-fundraiser-swift-sports-organisation-kampala</t>
+  </si>
+  <si>
+    <t>Finance Manager</t>
+  </si>
+  <si>
+    <t>Equality Federation</t>
+  </si>
+  <si>
+    <t>USD 91185.00 - 91185.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Human Rights Civil Liberties, Lgbtq</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e4275a0828ee4fad9c4f1049ce30e587-finance-manager-equality-federation-portland</t>
+  </si>
+  <si>
+    <t>Grants Manager</t>
+  </si>
+  <si>
+    <t>USD 101437.00 - 101437.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/95cc49c2134b4b20bd063d74fd38a059-grants-manager-equality-federation-portland</t>
+  </si>
+  <si>
+    <t>Groundskeeper (Part Time)</t>
+  </si>
+  <si>
+    <t>Historic Hudson Valley</t>
+  </si>
+  <si>
+    <t>Pocantico Hills, New York</t>
+  </si>
+  <si>
+    <t>USD 0.00 - 0.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8218acb118504b9aaf488ad9d250a31e-groundskeeper-part-time-historic-hudson-valley-pocantico-hills</t>
+  </si>
+  <si>
+    <t>Licensed Clinician-Worcester</t>
+  </si>
+  <si>
+    <t>HopeWell Inc.</t>
+  </si>
+  <si>
+    <t>Dedham, Massachusetts</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6a53ae3c8b54309b5a370098201a324-licensed-clinician-worcester-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>Literacy Interventionist, Full Time</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 66250.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/112f791379604d9c991e6755017422c0-literacy-interventionist-full-time-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>Literacy Interventionist, Part Time</t>
+  </si>
+  <si>
+    <t>USD 27.47 - 36.40/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2df3d781b089492d8d1732bc0efe2766-literacy-interventionist-part-time-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>MST Family Therapist</t>
+  </si>
+  <si>
+    <t>Youth Villages</t>
+  </si>
+  <si>
+    <t>Memphis, Tennessee</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 60000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f9a54d4f8734c779ba1a5d390d3a04c-mst-family-therapist-youth-villages-memphis</t>
+  </si>
+  <si>
+    <t>Multimedia Specialist</t>
+  </si>
+  <si>
+    <t>Defenders of Wildlife</t>
+  </si>
+  <si>
+    <t>USD 79000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Animals, Climate Change, Energy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c43efbea555f4d80b6baea3b4b6c5fdf-multimedia-specialist-defenders-of-wildlife-washington</t>
+  </si>
+  <si>
+    <t>Nonprofit Administrative Assistant</t>
+  </si>
+  <si>
+    <t>The Samuel Lawrence Foundation</t>
+  </si>
+  <si>
+    <t>Solana Beach, California</t>
+  </si>
+  <si>
+    <t>USD 26.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Arts Music</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2529a9bb925a46d9a53a1b87b8b372b4-nonprofit-administrative-assistant-the-samuel-lawrence-foundation-solana-beach</t>
+  </si>
+  <si>
+    <t>Office &amp; Meeting Coordinator</t>
+  </si>
+  <si>
+    <t>Bellarmine Jesuit Retreat House</t>
+  </si>
+  <si>
+    <t>Barrington, Illinois</t>
+  </si>
+  <si>
+    <t>USD 54000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Poverty, Religion Spirituality</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/869bb6ce894f459dbf81a55d571b1b61-office-meeting-coordinator-bellarmine-jesuit-retreat-house-barrington</t>
+  </si>
+  <si>
+    <t>OMRI is Hiring for a Bilingual Content Coordinator</t>
+  </si>
+  <si>
+    <t>Organic Materials Review Institute (OMRI)</t>
+  </si>
+  <si>
+    <t>USD 49765.00 - 54765.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c37fab73ef1e4f239c9d881fc34304d3-omri-is-hiring-for-a-bilingual-content-coordinator-organic-materials-review-institute-omri-eugene</t>
+  </si>
+  <si>
+    <t>Principal Paralegal</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3adb3dfef8dc40b6b990d35907b9f19c-principal-paralegal-the-wright-center-for-community-health-and-graduate-medical-education-scranton</t>
+  </si>
+  <si>
+    <t>Programs Officer, Scholars Programs</t>
+  </si>
+  <si>
+    <t>Newark, NJ</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 52000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0af5eabf3dce482d81361d7465232711-programs-officer-scholars-programs-seeds-access-changes-everything-newark</t>
+  </si>
+  <si>
+    <t>Project Manager, Social Services Job Training Program – Chicago, IL Region</t>
+  </si>
+  <si>
+    <t>Hunger Free America</t>
+  </si>
+  <si>
+    <t>USD 64000.00 - 64000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69204448549b47129d2fdbe775268801-project-manager-social-services-job-training-program-chicago-il-region-hunger-free-america-chicago</t>
+  </si>
+  <si>
+    <t>Regional Director, Development &amp; Philanthropy (Rochester Region)</t>
+  </si>
+  <si>
+    <t>Make-A-Wish Metro NY and Western NY</t>
+  </si>
+  <si>
+    <t>Rochester, New York</t>
+  </si>
+  <si>
+    <t>USD 88000.00 - 94000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c0ccf2285cf4f2fb7b512a96095f250-regional-director-development-philanthropy-rochester-region-make-a-wish-metro-ny-and-western-ny-rochester</t>
+  </si>
+  <si>
+    <t>Research and Monitoring Officer</t>
+  </si>
+  <si>
+    <t>Nature Foundation Sint Maarten</t>
+  </si>
+  <si>
+    <t>Cole Bay, (no state), SX</t>
+  </si>
+  <si>
+    <t>USD 2800.00 - 3300.00/month</t>
+  </si>
+  <si>
+    <t>Animals, Environment, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67d45d2faf0a4fe3964f693b54832740-research-and-monitoring-officer-nature-foundation-sint-maarten-cole-bay</t>
+  </si>
+  <si>
+    <t>Senior Attorney-Matrimonial Unit</t>
+  </si>
+  <si>
+    <t>District Council 37, Health &amp; Security Plan</t>
+  </si>
+  <si>
+    <t>USD 107515.00 - 130863.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Conflict Resolution, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/af91d275c19b4ba3bb4c2b4dc7365069-senior-attorney-matrimonial-unit-district-council-37-health-security-plan-new-york</t>
+  </si>
+  <si>
+    <t>Senior Director of Communications</t>
+  </si>
+  <si>
+    <t>Shalom Hartman Institute</t>
+  </si>
+  <si>
+    <t>USD 150000.00 - 175000.00/year</t>
+  </si>
+  <si>
+    <t>Religion Spirituality, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/12ed664dfc51449599156beca02be170-senior-director-of-communications-shalom-hartman-institute-new-york</t>
+  </si>
+  <si>
+    <t>Senior Fundraising Manager (fully remote)</t>
+  </si>
+  <si>
+    <t>New Left Accelerator</t>
+  </si>
+  <si>
+    <t>USD 44.70 - 52.16/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Entrepreneurship, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b3181d5b1ccc4418a02561598be09313-senior-fundraising-manager-fully-remote-new-left-accelerator-san-francisco</t>
+  </si>
+  <si>
+    <t>Service Enriched Housing Super Hero</t>
+  </si>
+  <si>
+    <t>Community Housing Resource Partners, Inc.</t>
+  </si>
+  <si>
+    <t>San Antonio, Texas</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 16.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Financial Literacy Personal Finance, Seniors Retirement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67947df35ae84f8db27cfe64e0b7a561-service-enriched-housing-super-hero-community-housing-resource-partners-inc-san-antonio</t>
+  </si>
+  <si>
+    <t>USD 16.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>Community Development, Education, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2e9b07e4f07a412f8cab4c61910fb746-service-enriched-housing-super-hero-community-housing-resource-partners-inc-san-antonio</t>
+  </si>
+  <si>
+    <t>Shared Living Coordinator</t>
+  </si>
+  <si>
+    <t>USD 50000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c03e820ee4cd4c0dafde83c7b3f7dab8-shared-living-coordinator-hopewell-inc-dedham</t>
+  </si>
+  <si>
+    <t>Small Animals Coordinator at Ambue Ari Sanctuary – Work with Rescued Wildlife in the Bolivian Rainforest</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b82cf7ef7229428e854d6625aa052f98-small-animals-coordinator-at-ambue-ari-sanctuary-work-with-rescued-wildlife-in-the-bolivian-rainforest-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
+  </si>
+  <si>
+    <t>Social Media &amp; Content Manager</t>
+  </si>
+  <si>
+    <t>Civic Ventures</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Economic Development, Job Workplace, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/business-job/b7c2c916792844ef986ea52958708e47-social-media-content-manager-civic-ventures-seattle</t>
+  </si>
+  <si>
+    <t>Staff Attorney</t>
+  </si>
+  <si>
+    <t>The Waterfront Project, Inc.</t>
+  </si>
+  <si>
+    <t>Jersey City, New Jersey</t>
+  </si>
+  <si>
+    <t>USD 82500.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7850e64733824a24a2db122e5ce1e973-staff-attorney-the-waterfront-project-inc-jersey-city</t>
+  </si>
+  <si>
+    <t>Staff Attorney-Housing Unit</t>
+  </si>
+  <si>
+    <t>USD 73270.00 - 104637.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Conflict Resolution, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7fd999ad3d614d20ba72f9cffdf79f99-staff-attorney-housing-unit-district-council-37-health-security-plan-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney-MELS Matrimonial Unit</t>
+  </si>
+  <si>
+    <t>Family, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fabbe8f2b3f44655ad81b03fe0ddf3bb-staff-attorney-mels-matrimonial-unit-district-council-37-health-security-plan-new-york</t>
+  </si>
+  <si>
+    <t>Steve Lagerstrom</t>
+  </si>
+  <si>
+    <t>The Battery Conservancy</t>
+  </si>
+  <si>
+    <t>New York, NY</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/583738eea22d46bcbea50177767eaad7-steve-lagerstrom-the-battery-conservancy-new-york</t>
+  </si>
+  <si>
+    <t>Team Leader - Hotlines</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 69750.00/year</t>
+  </si>
+  <si>
+    <t>Sexual Abuse Human Trafficking, Family, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3f52439cb9774c74b660af6c8f9cf2f4-team-leader-hotlines-safe-horizon-new-york</t>
+  </si>
+  <si>
+    <t>TÉRMINOS DE REFERENCIA ENCUESTADOR(A): Ciudad Juárez, Chihuahua</t>
+  </si>
+  <si>
+    <t>Medicos del Mundo Francia Mexico, AC</t>
+  </si>
+  <si>
+    <t>Juárez, Chihuahua, MX</t>
+  </si>
+  <si>
+    <t>Environment, Immigrants Or Refugees, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/793f406c36f74194af6f5a120f9c4511-terminos-de-referencia-encuestadora-ciudad-juarez-chihuahua-medicos-del-mundo-francia-mexico-ac-juarez</t>
+  </si>
+  <si>
+    <t>Trauma Counselor - SWF</t>
+  </si>
+  <si>
+    <t>USD 62000.00 - 65000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99b052d70ed74e36a6f9a063e884b6c8-trauma-counselor-swf-safe-horizon-staten-island</t>
+  </si>
+  <si>
+    <t>Warehouse Operations Manager</t>
+  </si>
+  <si>
+    <t>Food Lifeline</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 46.00/hour</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c726d95a92ad421d99fa6e1f42010498-warehouse-operations-manager-food-lifeline-seattle</t>
+  </si>
+  <si>
+    <t>Zona: Mar del Plata - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
+  </si>
+  <si>
+    <t>Aldeas Infantiles SOS Argentina</t>
+  </si>
+  <si>
+    <t>Mar del Plata, Provincia de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/24d88beee0aa4c35b63b366a17a25c8d-zona-mar-del-plata-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-mar-del-plata</t>
+  </si>
+  <si>
+    <t>Zona: Rosario - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
+  </si>
+  <si>
+    <t>Rosario, Santa Fe, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0e04713cc40d4ed591b8d135a8af80b3-zona-rosario-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-rosario</t>
+  </si>
+  <si>
+    <t>Zona: San Miguel de Tucumán - Lider de Equipo de Captadores/as de Fondos (F2F)</t>
+  </si>
+  <si>
+    <t>San Miguel de Tucumán, Tucumán, AR</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3869ae7c41f9468ba61c5a47881bda54-zona-san-miguel-de-tucuman-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-san-miguel-de-tucuman</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -54,6 +1512,10 @@
     </font>
     <font>
       <b/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF1155CC"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,9 +1538,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -418,7 +1881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -457,8 +1920,778 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C10" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="C12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" t="s">
+        <v>72</v>
+      </c>
+      <c r="F12" t="s">
+        <v>73</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+      <c r="B14" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" t="s">
+        <v>85</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B15" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F15" t="s">
+        <v>85</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>98</v>
+      </c>
+      <c r="E17" t="s">
+        <v>99</v>
+      </c>
+      <c r="F17" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" t="s">
+        <v>105</v>
+      </c>
+      <c r="F18" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" t="s">
+        <v>110</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
+        <v>115</v>
+      </c>
+      <c r="D20" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" t="s">
+        <v>116</v>
+      </c>
+      <c r="F20" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F21" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>123</v>
+      </c>
+      <c r="B22" t="s">
+        <v>124</v>
+      </c>
+      <c r="C22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" t="s">
+        <v>127</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" t="s">
+        <v>130</v>
+      </c>
+      <c r="C23" t="s">
+        <v>131</v>
+      </c>
+      <c r="D23" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" t="s">
+        <v>132</v>
+      </c>
+      <c r="F23" t="s">
+        <v>133</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
+        <v>138</v>
+      </c>
+      <c r="F24" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" t="s">
+        <v>144</v>
+      </c>
+      <c r="F25" t="s">
+        <v>145</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>147</v>
+      </c>
+      <c r="B26" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" t="s">
+        <v>149</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" t="s">
+        <v>151</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>153</v>
+      </c>
+      <c r="B27" t="s">
+        <v>154</v>
+      </c>
+      <c r="C27" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" t="s">
+        <v>159</v>
+      </c>
+      <c r="C28" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F28" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" t="s">
+        <v>164</v>
+      </c>
+      <c r="C29" t="s">
+        <v>165</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" t="s">
+        <v>166</v>
+      </c>
+      <c r="F29" t="s">
+        <v>167</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B30" t="s">
+        <v>170</v>
+      </c>
+      <c r="C30" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" t="s">
+        <v>71</v>
+      </c>
+      <c r="E30" t="s">
+        <v>171</v>
+      </c>
+      <c r="F30" t="s">
+        <v>172</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D31" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" t="s">
+        <v>176</v>
+      </c>
+      <c r="F31" t="s">
+        <v>177</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D32" t="s">
+        <v>98</v>
+      </c>
+      <c r="E32" t="s">
+        <v>181</v>
+      </c>
+      <c r="F32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" t="s">
+        <v>185</v>
+      </c>
+      <c r="C33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" t="s">
+        <v>187</v>
+      </c>
+      <c r="F33" t="s">
+        <v>177</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -514,7 +2747,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -553,8 +2786,1498 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E4" t="s">
+        <v>206</v>
+      </c>
+      <c r="F4" t="s">
+        <v>207</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" t="s">
+        <v>199</v>
+      </c>
+      <c r="E5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B7" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" t="s">
+        <v>223</v>
+      </c>
+      <c r="F7" t="s">
+        <v>224</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" t="s">
+        <v>230</v>
+      </c>
+      <c r="F8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>233</v>
+      </c>
+      <c r="B9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" t="s">
+        <v>199</v>
+      </c>
+      <c r="E9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" t="s">
+        <v>213</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>237</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D10" t="s">
+        <v>199</v>
+      </c>
+      <c r="E10" t="s">
+        <v>240</v>
+      </c>
+      <c r="F10" t="s">
+        <v>206</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>242</v>
+      </c>
+      <c r="B11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C11" t="s">
+        <v>244</v>
+      </c>
+      <c r="D11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" t="s">
+        <v>194</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>247</v>
+      </c>
+      <c r="B12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C12" t="s">
+        <v>249</v>
+      </c>
+      <c r="D12" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" t="s">
+        <v>250</v>
+      </c>
+      <c r="F12" t="s">
+        <v>251</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C13" t="s">
+        <v>255</v>
+      </c>
+      <c r="D13" t="s">
+        <v>199</v>
+      </c>
+      <c r="E13" t="s">
+        <v>256</v>
+      </c>
+      <c r="F13" t="s">
+        <v>194</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" t="s">
+        <v>199</v>
+      </c>
+      <c r="E14" t="s">
+        <v>261</v>
+      </c>
+      <c r="F14" t="s">
+        <v>262</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>264</v>
+      </c>
+      <c r="B15" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" t="s">
+        <v>199</v>
+      </c>
+      <c r="E15" t="s">
+        <v>266</v>
+      </c>
+      <c r="F15" t="s">
+        <v>267</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" t="s">
+        <v>270</v>
+      </c>
+      <c r="C16" t="s">
+        <v>271</v>
+      </c>
+      <c r="D16" t="s">
+        <v>199</v>
+      </c>
+      <c r="E16" t="s">
+        <v>272</v>
+      </c>
+      <c r="F16" t="s">
+        <v>273</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>275</v>
+      </c>
+      <c r="B17" t="s">
+        <v>276</v>
+      </c>
+      <c r="C17" t="s">
+        <v>222</v>
+      </c>
+      <c r="D17" t="s">
+        <v>218</v>
+      </c>
+      <c r="E17" t="s">
+        <v>277</v>
+      </c>
+      <c r="F17" t="s">
+        <v>213</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B18" t="s">
+        <v>280</v>
+      </c>
+      <c r="C18" t="s">
+        <v>281</v>
+      </c>
+      <c r="D18" t="s">
+        <v>199</v>
+      </c>
+      <c r="E18" t="s">
+        <v>282</v>
+      </c>
+      <c r="F18" t="s">
+        <v>224</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>284</v>
+      </c>
+      <c r="B19" t="s">
+        <v>285</v>
+      </c>
+      <c r="C19" t="s">
+        <v>222</v>
+      </c>
+      <c r="D19" t="s">
+        <v>199</v>
+      </c>
+      <c r="E19" t="s">
+        <v>286</v>
+      </c>
+      <c r="F19" t="s">
+        <v>206</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>288</v>
+      </c>
+      <c r="B20" t="s">
+        <v>289</v>
+      </c>
+      <c r="C20" t="s">
+        <v>290</v>
+      </c>
+      <c r="D20" t="s">
+        <v>199</v>
+      </c>
+      <c r="E20" t="s">
+        <v>291</v>
+      </c>
+      <c r="F20" t="s">
+        <v>292</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>294</v>
+      </c>
+      <c r="B21" t="s">
+        <v>295</v>
+      </c>
+      <c r="C21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E21" t="s">
+        <v>297</v>
+      </c>
+      <c r="F21" t="s">
+        <v>298</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>300</v>
+      </c>
+      <c r="B22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C22" t="s">
+        <v>255</v>
+      </c>
+      <c r="D22" t="s">
+        <v>229</v>
+      </c>
+      <c r="E22" t="s">
+        <v>302</v>
+      </c>
+      <c r="F22" t="s">
+        <v>206</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>304</v>
+      </c>
+      <c r="B23" t="s">
+        <v>305</v>
+      </c>
+      <c r="C23" t="s">
+        <v>306</v>
+      </c>
+      <c r="D23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E23" t="s">
+        <v>307</v>
+      </c>
+      <c r="F23" t="s">
+        <v>308</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>310</v>
+      </c>
+      <c r="B24" t="s">
+        <v>295</v>
+      </c>
+      <c r="C24" t="s">
+        <v>296</v>
+      </c>
+      <c r="D24" t="s">
+        <v>199</v>
+      </c>
+      <c r="E24" t="s">
+        <v>311</v>
+      </c>
+      <c r="F24" t="s">
+        <v>298</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B25" t="s">
+        <v>314</v>
+      </c>
+      <c r="C25" t="s">
+        <v>315</v>
+      </c>
+      <c r="D25" t="s">
+        <v>316</v>
+      </c>
+      <c r="E25" t="s">
+        <v>317</v>
+      </c>
+      <c r="F25" t="s">
+        <v>318</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>320</v>
+      </c>
+      <c r="B26" t="s">
+        <v>321</v>
+      </c>
+      <c r="C26" t="s">
+        <v>322</v>
+      </c>
+      <c r="D26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E26" t="s">
+        <v>323</v>
+      </c>
+      <c r="F26" t="s">
+        <v>324</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>326</v>
+      </c>
+      <c r="B27" t="s">
+        <v>327</v>
+      </c>
+      <c r="C27" t="s">
+        <v>328</v>
+      </c>
+      <c r="D27" t="s">
+        <v>199</v>
+      </c>
+      <c r="E27" t="s">
+        <v>329</v>
+      </c>
+      <c r="F27" t="s">
+        <v>330</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" t="s">
+        <v>334</v>
+      </c>
+      <c r="D28" t="s">
+        <v>316</v>
+      </c>
+      <c r="E28" t="s">
+        <v>335</v>
+      </c>
+      <c r="F28" t="s">
+        <v>336</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>338</v>
+      </c>
+      <c r="B29" t="s">
+        <v>339</v>
+      </c>
+      <c r="C29" t="s">
+        <v>334</v>
+      </c>
+      <c r="D29" t="s">
+        <v>199</v>
+      </c>
+      <c r="E29" t="s">
+        <v>340</v>
+      </c>
+      <c r="F29" t="s">
+        <v>341</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>343</v>
+      </c>
+      <c r="B30" t="s">
+        <v>339</v>
+      </c>
+      <c r="C30" t="s">
+        <v>334</v>
+      </c>
+      <c r="D30" t="s">
+        <v>199</v>
+      </c>
+      <c r="E30" t="s">
+        <v>344</v>
+      </c>
+      <c r="F30" t="s">
+        <v>341</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>346</v>
+      </c>
+      <c r="B31" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" t="s">
+        <v>348</v>
+      </c>
+      <c r="D31" t="s">
+        <v>218</v>
+      </c>
+      <c r="E31" t="s">
+        <v>349</v>
+      </c>
+      <c r="F31" t="s">
+        <v>206</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>351</v>
+      </c>
+      <c r="B32" t="s">
+        <v>352</v>
+      </c>
+      <c r="C32" t="s">
+        <v>353</v>
+      </c>
+      <c r="D32" t="s">
+        <v>199</v>
+      </c>
+      <c r="E32" t="s">
+        <v>329</v>
+      </c>
+      <c r="F32" t="s">
+        <v>354</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>356</v>
+      </c>
+      <c r="B33" t="s">
+        <v>352</v>
+      </c>
+      <c r="C33" t="s">
+        <v>353</v>
+      </c>
+      <c r="D33" t="s">
+        <v>199</v>
+      </c>
+      <c r="E33" t="s">
+        <v>357</v>
+      </c>
+      <c r="F33" t="s">
+        <v>354</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>359</v>
+      </c>
+      <c r="B34" t="s">
+        <v>352</v>
+      </c>
+      <c r="C34" t="s">
+        <v>353</v>
+      </c>
+      <c r="D34" t="s">
+        <v>218</v>
+      </c>
+      <c r="E34" t="s">
+        <v>360</v>
+      </c>
+      <c r="F34" t="s">
+        <v>354</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>362</v>
+      </c>
+      <c r="B35" t="s">
+        <v>363</v>
+      </c>
+      <c r="C35" t="s">
+        <v>364</v>
+      </c>
+      <c r="D35" t="s">
+        <v>199</v>
+      </c>
+      <c r="E35" t="s">
+        <v>365</v>
+      </c>
+      <c r="F35" t="s">
+        <v>366</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>368</v>
+      </c>
+      <c r="B36" t="s">
+        <v>369</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36" t="s">
+        <v>199</v>
+      </c>
+      <c r="E36" t="s">
+        <v>370</v>
+      </c>
+      <c r="F36" t="s">
+        <v>371</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>373</v>
+      </c>
+      <c r="B37" t="s">
+        <v>374</v>
+      </c>
+      <c r="C37" t="s">
+        <v>375</v>
+      </c>
+      <c r="D37" t="s">
+        <v>218</v>
+      </c>
+      <c r="E37" t="s">
+        <v>376</v>
+      </c>
+      <c r="F37" t="s">
+        <v>377</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>379</v>
+      </c>
+      <c r="B38" t="s">
+        <v>380</v>
+      </c>
+      <c r="C38" t="s">
+        <v>381</v>
+      </c>
+      <c r="D38" t="s">
+        <v>199</v>
+      </c>
+      <c r="E38" t="s">
+        <v>382</v>
+      </c>
+      <c r="F38" t="s">
+        <v>383</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>385</v>
+      </c>
+      <c r="B39" t="s">
+        <v>386</v>
+      </c>
+      <c r="C39" t="s">
+        <v>334</v>
+      </c>
+      <c r="D39" t="s">
+        <v>199</v>
+      </c>
+      <c r="E39" t="s">
+        <v>387</v>
+      </c>
+      <c r="F39" t="s">
+        <v>388</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>390</v>
+      </c>
+      <c r="B40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C40" t="s">
+        <v>205</v>
+      </c>
+      <c r="D40" t="s">
+        <v>199</v>
+      </c>
+      <c r="E40" t="s">
+        <v>206</v>
+      </c>
+      <c r="F40" t="s">
+        <v>207</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>392</v>
+      </c>
+      <c r="B41" t="s">
+        <v>190</v>
+      </c>
+      <c r="C41" t="s">
+        <v>393</v>
+      </c>
+      <c r="D41" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" t="s">
+        <v>394</v>
+      </c>
+      <c r="F41" t="s">
+        <v>194</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>396</v>
+      </c>
+      <c r="B42" t="s">
+        <v>397</v>
+      </c>
+      <c r="C42" t="s">
+        <v>255</v>
+      </c>
+      <c r="D42" t="s">
+        <v>199</v>
+      </c>
+      <c r="E42" t="s">
+        <v>398</v>
+      </c>
+      <c r="F42" t="s">
+        <v>399</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>401</v>
+      </c>
+      <c r="B43" t="s">
+        <v>402</v>
+      </c>
+      <c r="C43" t="s">
+        <v>403</v>
+      </c>
+      <c r="D43" t="s">
+        <v>199</v>
+      </c>
+      <c r="E43" t="s">
+        <v>404</v>
+      </c>
+      <c r="F43" t="s">
+        <v>405</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>407</v>
+      </c>
+      <c r="B44" t="s">
+        <v>408</v>
+      </c>
+      <c r="C44" t="s">
+        <v>409</v>
+      </c>
+      <c r="D44" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" t="s">
+        <v>410</v>
+      </c>
+      <c r="F44" t="s">
+        <v>411</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>413</v>
+      </c>
+      <c r="B45" t="s">
+        <v>414</v>
+      </c>
+      <c r="C45" t="s">
+        <v>222</v>
+      </c>
+      <c r="D45" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" t="s">
+        <v>415</v>
+      </c>
+      <c r="F45" t="s">
+        <v>416</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>418</v>
+      </c>
+      <c r="B46" t="s">
+        <v>419</v>
+      </c>
+      <c r="C46" t="s">
+        <v>222</v>
+      </c>
+      <c r="D46" t="s">
+        <v>199</v>
+      </c>
+      <c r="E46" t="s">
+        <v>420</v>
+      </c>
+      <c r="F46" t="s">
+        <v>421</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>423</v>
+      </c>
+      <c r="B47" t="s">
+        <v>424</v>
+      </c>
+      <c r="C47" t="s">
+        <v>334</v>
+      </c>
+      <c r="D47" t="s">
+        <v>218</v>
+      </c>
+      <c r="E47" t="s">
+        <v>425</v>
+      </c>
+      <c r="F47" t="s">
+        <v>426</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>428</v>
+      </c>
+      <c r="B48" t="s">
+        <v>429</v>
+      </c>
+      <c r="C48" t="s">
+        <v>430</v>
+      </c>
+      <c r="D48" t="s">
+        <v>218</v>
+      </c>
+      <c r="E48" t="s">
+        <v>431</v>
+      </c>
+      <c r="F48" t="s">
+        <v>432</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>428</v>
+      </c>
+      <c r="B49" t="s">
+        <v>429</v>
+      </c>
+      <c r="C49" t="s">
+        <v>430</v>
+      </c>
+      <c r="D49" t="s">
+        <v>199</v>
+      </c>
+      <c r="E49" t="s">
+        <v>434</v>
+      </c>
+      <c r="F49" t="s">
+        <v>435</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>437</v>
+      </c>
+      <c r="B50" t="s">
+        <v>352</v>
+      </c>
+      <c r="C50" t="s">
+        <v>353</v>
+      </c>
+      <c r="D50" t="s">
+        <v>199</v>
+      </c>
+      <c r="E50" t="s">
+        <v>438</v>
+      </c>
+      <c r="F50" t="s">
+        <v>354</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>440</v>
+      </c>
+      <c r="B51" t="s">
+        <v>270</v>
+      </c>
+      <c r="C51" t="s">
+        <v>271</v>
+      </c>
+      <c r="D51" t="s">
+        <v>199</v>
+      </c>
+      <c r="E51" t="s">
+        <v>272</v>
+      </c>
+      <c r="F51" t="s">
+        <v>273</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>442</v>
+      </c>
+      <c r="B52" t="s">
+        <v>443</v>
+      </c>
+      <c r="C52" t="s">
+        <v>444</v>
+      </c>
+      <c r="D52" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" t="s">
+        <v>445</v>
+      </c>
+      <c r="F52" t="s">
+        <v>446</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>448</v>
+      </c>
+      <c r="B53" t="s">
+        <v>449</v>
+      </c>
+      <c r="C53" t="s">
+        <v>450</v>
+      </c>
+      <c r="D53" t="s">
+        <v>199</v>
+      </c>
+      <c r="E53" t="s">
+        <v>451</v>
+      </c>
+      <c r="F53" t="s">
+        <v>452</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>454</v>
+      </c>
+      <c r="B54" t="s">
+        <v>414</v>
+      </c>
+      <c r="C54" t="s">
+        <v>222</v>
+      </c>
+      <c r="D54" t="s">
+        <v>199</v>
+      </c>
+      <c r="E54" t="s">
+        <v>455</v>
+      </c>
+      <c r="F54" t="s">
+        <v>456</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>458</v>
+      </c>
+      <c r="B55" t="s">
+        <v>414</v>
+      </c>
+      <c r="C55" t="s">
+        <v>222</v>
+      </c>
+      <c r="D55" t="s">
+        <v>199</v>
+      </c>
+      <c r="E55" t="s">
+        <v>455</v>
+      </c>
+      <c r="F55" t="s">
+        <v>459</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>461</v>
+      </c>
+      <c r="B56" t="s">
+        <v>462</v>
+      </c>
+      <c r="C56" t="s">
+        <v>463</v>
+      </c>
+      <c r="D56" t="s">
+        <v>199</v>
+      </c>
+      <c r="E56" t="s">
+        <v>464</v>
+      </c>
+      <c r="F56" t="s">
+        <v>206</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>466</v>
+      </c>
+      <c r="B57" t="s">
+        <v>259</v>
+      </c>
+      <c r="C57" t="s">
+        <v>222</v>
+      </c>
+      <c r="D57" t="s">
+        <v>199</v>
+      </c>
+      <c r="E57" t="s">
+        <v>467</v>
+      </c>
+      <c r="F57" t="s">
+        <v>468</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>470</v>
+      </c>
+      <c r="B58" t="s">
+        <v>471</v>
+      </c>
+      <c r="C58" t="s">
+        <v>472</v>
+      </c>
+      <c r="D58" t="s">
+        <v>218</v>
+      </c>
+      <c r="E58" t="s">
+        <v>206</v>
+      </c>
+      <c r="F58" t="s">
+        <v>473</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>475</v>
+      </c>
+      <c r="B59" t="s">
+        <v>259</v>
+      </c>
+      <c r="C59" t="s">
+        <v>265</v>
+      </c>
+      <c r="D59" t="s">
+        <v>199</v>
+      </c>
+      <c r="E59" t="s">
+        <v>476</v>
+      </c>
+      <c r="F59" t="s">
+        <v>267</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>478</v>
+      </c>
+      <c r="B60" t="s">
+        <v>479</v>
+      </c>
+      <c r="C60" t="s">
+        <v>444</v>
+      </c>
+      <c r="D60" t="s">
+        <v>199</v>
+      </c>
+      <c r="E60" t="s">
+        <v>480</v>
+      </c>
+      <c r="F60" t="s">
+        <v>481</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>483</v>
+      </c>
+      <c r="B61" t="s">
+        <v>484</v>
+      </c>
+      <c r="C61" t="s">
+        <v>485</v>
+      </c>
+      <c r="D61" t="s">
+        <v>218</v>
+      </c>
+      <c r="E61" t="s">
+        <v>206</v>
+      </c>
+      <c r="F61" t="s">
+        <v>486</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>488</v>
+      </c>
+      <c r="B62" t="s">
+        <v>484</v>
+      </c>
+      <c r="C62" t="s">
+        <v>489</v>
+      </c>
+      <c r="D62" t="s">
+        <v>218</v>
+      </c>
+      <c r="E62" t="s">
+        <v>206</v>
+      </c>
+      <c r="F62" t="s">
+        <v>486</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>491</v>
+      </c>
+      <c r="B63" t="s">
+        <v>484</v>
+      </c>
+      <c r="C63" t="s">
+        <v>492</v>
+      </c>
+      <c r="D63" t="s">
+        <v>218</v>
+      </c>
+      <c r="E63" t="s">
+        <v>206</v>
+      </c>
+      <c r="F63" t="s">
+        <v>486</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>493</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="H3" r:id="rId2"/>
+    <hyperlink ref="H4" r:id="rId3"/>
+    <hyperlink ref="H5" r:id="rId4"/>
+    <hyperlink ref="H6" r:id="rId5"/>
+    <hyperlink ref="H7" r:id="rId6"/>
+    <hyperlink ref="H8" r:id="rId7"/>
+    <hyperlink ref="H9" r:id="rId8"/>
+    <hyperlink ref="H10" r:id="rId9"/>
+    <hyperlink ref="H11" r:id="rId10"/>
+    <hyperlink ref="H12" r:id="rId11"/>
+    <hyperlink ref="H13" r:id="rId12"/>
+    <hyperlink ref="H14" r:id="rId13"/>
+    <hyperlink ref="H15" r:id="rId14"/>
+    <hyperlink ref="H16" r:id="rId15"/>
+    <hyperlink ref="H17" r:id="rId16"/>
+    <hyperlink ref="H18" r:id="rId17"/>
+    <hyperlink ref="H19" r:id="rId18"/>
+    <hyperlink ref="H20" r:id="rId19"/>
+    <hyperlink ref="H21" r:id="rId20"/>
+    <hyperlink ref="H22" r:id="rId21"/>
+    <hyperlink ref="H23" r:id="rId22"/>
+    <hyperlink ref="H24" r:id="rId23"/>
+    <hyperlink ref="H25" r:id="rId24"/>
+    <hyperlink ref="H26" r:id="rId25"/>
+    <hyperlink ref="H27" r:id="rId26"/>
+    <hyperlink ref="H28" r:id="rId27"/>
+    <hyperlink ref="H29" r:id="rId28"/>
+    <hyperlink ref="H30" r:id="rId29"/>
+    <hyperlink ref="H31" r:id="rId30"/>
+    <hyperlink ref="H32" r:id="rId31"/>
+    <hyperlink ref="H33" r:id="rId32"/>
+    <hyperlink ref="H34" r:id="rId33"/>
+    <hyperlink ref="H35" r:id="rId34"/>
+    <hyperlink ref="H36" r:id="rId35"/>
+    <hyperlink ref="H37" r:id="rId36"/>
+    <hyperlink ref="H38" r:id="rId37"/>
+    <hyperlink ref="H39" r:id="rId38"/>
+    <hyperlink ref="H40" r:id="rId39"/>
+    <hyperlink ref="H41" r:id="rId40"/>
+    <hyperlink ref="H42" r:id="rId41"/>
+    <hyperlink ref="H43" r:id="rId42"/>
+    <hyperlink ref="H44" r:id="rId43"/>
+    <hyperlink ref="H45" r:id="rId44"/>
+    <hyperlink ref="H46" r:id="rId45"/>
+    <hyperlink ref="H47" r:id="rId46"/>
+    <hyperlink ref="H48" r:id="rId47"/>
+    <hyperlink ref="H49" r:id="rId48"/>
+    <hyperlink ref="H50" r:id="rId49"/>
+    <hyperlink ref="H51" r:id="rId50"/>
+    <hyperlink ref="H52" r:id="rId51"/>
+    <hyperlink ref="H53" r:id="rId52"/>
+    <hyperlink ref="H54" r:id="rId53"/>
+    <hyperlink ref="H55" r:id="rId54"/>
+    <hyperlink ref="H56" r:id="rId55"/>
+    <hyperlink ref="H57" r:id="rId56"/>
+    <hyperlink ref="H58" r:id="rId57"/>
+    <hyperlink ref="H59" r:id="rId58"/>
+    <hyperlink ref="H60" r:id="rId59"/>
+    <hyperlink ref="H61" r:id="rId60"/>
+    <hyperlink ref="H62" r:id="rId61"/>
+    <hyperlink ref="H63" r:id="rId62"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>

--- a/docs/xlsx/jobs-2026-09-03.xlsx
+++ b/docs/xlsx/jobs-2026-09-03.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="853">
   <si>
     <t>Title</t>
   </si>
@@ -604,6 +604,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/6b94edb33f6044fb8b38114d53dba642-academic-teacher-seeds-access-changes-everything-livingston</t>
   </si>
   <si>
+    <t>Administrative Operations Manager</t>
+  </si>
+  <si>
+    <t>Snoqualmie Valley Food Bank</t>
+  </si>
+  <si>
+    <t>North Bend, Washington</t>
+  </si>
+  <si>
+    <t>Full Time</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Family, Hunger Food Security, Rural Areas</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/9a3f3089d35041d59b8451634d476454-administrative-operations-manager-snoqualmie-valley-food-bank-north-bend</t>
+  </si>
+  <si>
     <t>Advocate - Education</t>
   </si>
   <si>
@@ -613,9 +634,6 @@
     <t>LANSING, MI</t>
   </si>
   <si>
-    <t>Full Time</t>
-  </si>
-  <si>
     <t>USD 58000.00 - 62000.00/year</t>
   </si>
   <si>
@@ -625,6 +643,63 @@
     <t>https://www.idealist.org/en/nonprofit-job/1d12acaec2eb44abb6d73eb4565f5e3c-advocate-education-disability-rights-michigan-lansing</t>
   </si>
   <si>
+    <t>An Experienced Immigration Paralegal/Administrative Assistant Needed Part-time leading to Full-time</t>
+  </si>
+  <si>
+    <t>The Ansob Center for Refugees</t>
+  </si>
+  <si>
+    <t>ASTORIA, NEW YORK</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>USD 22.00 - 24.00/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Legal Assistance, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8affd7b20c9a4702bfc0eb70243d52ad-an-experienced-immigration-paralegaladministrative-assistant-needed-part-time-leading-to-full-time-the-ansob-center-for-refugees-astoria</t>
+  </si>
+  <si>
+    <t>Analista de Performance (Marketing Digital) para oficinas MSF LAT</t>
+  </si>
+  <si>
+    <t>MÉDICOS SIN FRONTERAS LAT</t>
+  </si>
+  <si>
+    <t>Buenos Aires, Ciudad Autónoma de Buenos Aires, AR</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Disaster Relief, Health Medicine, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c5d834256ad4b01bc5bc78db4d4a34d-analista-de-performance-marketing-digital-para-oficinas-msf-lat-medicos-sin-fronteras-lat-buenos-aires</t>
+  </si>
+  <si>
+    <t>Assistant Community Engagement Coordinator</t>
+  </si>
+  <si>
+    <t>CT LEAD (Leaders Education Advocacy and Diversity)</t>
+  </si>
+  <si>
+    <t>Norwich, Connecticut</t>
+  </si>
+  <si>
+    <t>USD 27.00 - 27.00/hour</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7b97c997267c410388c86df2c8f27a20-assistant-community-engagement-coordinator-ct-lead-leaders-education-advocacy-and-diversity-norwich</t>
+  </si>
+  <si>
     <t>Associate Counsel</t>
   </si>
   <si>
@@ -634,15 +709,45 @@
     <t>Scranton, Pennsylvania</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>Children Youth, Community Development, Health Medicine</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/6f0e03181a5b443fb5440250d38a4220-associate-counsel-the-wright-center-for-community-health-and-graduate-medical-education-scranton</t>
   </si>
   <si>
+    <t>Associate Director, Data Hub</t>
+  </si>
+  <si>
+    <t>Project Evident</t>
+  </si>
+  <si>
+    <t>Remote (Boston, Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 105000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Education, Philanthropy, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/608ae3c561124efa84a3afeee75a35ac-associate-director-data-hub-project-evident-boston</t>
+  </si>
+  <si>
+    <t>Associate for Nonprofit Executive Search Firm (REMOTE BASED IN DMV)</t>
+  </si>
+  <si>
+    <t>Good Insight</t>
+  </si>
+  <si>
+    <t>Remote (Washington, District of Columbia)</t>
+  </si>
+  <si>
+    <t>USD 60000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/3eee716fbe364bbe87180cab4980062d-associate-for-nonprofit-executive-search-firm-remote-based-in-dmv-good-insight-washington</t>
+  </si>
+  <si>
     <t>Associate Vice President of Marketing &amp; Communications</t>
   </si>
   <si>
@@ -661,6 +766,36 @@
     <t>https://www.idealist.org/en/nonprofit-job/39c8dabe28a747e9b441a84d478a730e-associate-vice-president-of-marketing-communications-levine-music-washington</t>
   </si>
   <si>
+    <t>ATTAIN Lab Coordinator, NYC - Queens</t>
+  </si>
+  <si>
+    <t>The Research Foundation For SUNY</t>
+  </si>
+  <si>
+    <t>Queens, New York</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/dc0b1ca1f17f44439849aef3d2e33529-attain-lab-coordinator-nyc-queens-the-research-foundation-for-suny-queens</t>
+  </si>
+  <si>
+    <t>Bilingual Aftercare Specialist (English/Spanish) (SHARE)</t>
+  </si>
+  <si>
+    <t>Anthos Home</t>
+  </si>
+  <si>
+    <t>New York, New York</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 70000.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/012edc6c2e374fbca8af1e3ec83debdc-bilingual-aftercare-specialist-englishspanish-share-anthos-home-new-york</t>
+  </si>
+  <si>
     <t>Bookkeeper</t>
   </si>
   <si>
@@ -670,9 +805,6 @@
     <t>Philadelphia, Pennsylvania</t>
   </si>
   <si>
-    <t>Part Time</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/985b2ea0eef74b488767d9c3924d8d83-bookkeeper-dawns-place-philadelphia</t>
   </si>
   <si>
@@ -682,9 +814,6 @@
     <t>Literacy Inc. (LINC)</t>
   </si>
   <si>
-    <t>New York, New York</t>
-  </si>
-  <si>
     <t>USD 60000.00 - 70000.00/year</t>
   </si>
   <si>
@@ -742,6 +871,24 @@
     <t>https://www.idealist.org/en/job/caeae787770f4fa68f2cc7a7d086c1b1-career-coach-wioa-ser-metro-detroit-detroit</t>
   </si>
   <si>
+    <t>Caregiver Support Specialist</t>
+  </si>
+  <si>
+    <t>Amara</t>
+  </si>
+  <si>
+    <t>Seattle, Washington</t>
+  </si>
+  <si>
+    <t>USD 30.65 - 34.66/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/442f37dcd5564cad9460abd72009cc6b-caregiver-support-specialist-amara-seattle</t>
+  </si>
+  <si>
     <t>Castlemont Community Initiatives Senior Manager</t>
   </si>
   <si>
@@ -823,6 +970,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/5407c93603cd48c490a479ef80054df3-clinical-partner-intimate-partner-violence-ipv-safe-horizon-staten-island</t>
   </si>
   <si>
+    <t>Communications Associate</t>
+  </si>
+  <si>
+    <t>Platform for Social Impact</t>
+  </si>
+  <si>
+    <t>San Juan, San Juan, PR</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 50000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Economic Development, Family</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ce30210d7f040d7a51b1bc79097de36-communications-associate-platform-for-social-impact-san-juan</t>
+  </si>
+  <si>
+    <t>Community Safety Community Organizer</t>
+  </si>
+  <si>
+    <t>Jewish Council on Urban Affairs</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 57000.00/year</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Civic Engagement, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/33579faf8b28430599726683be673a6a-community-safety-community-organizer-jewish-council-on-urban-affairs-chicago</t>
+  </si>
+  <si>
+    <t>Conservation Policy Analyst</t>
+  </si>
+  <si>
+    <t>Xerces Society Inc</t>
+  </si>
+  <si>
+    <t>Remote (Oregon)</t>
+  </si>
+  <si>
+    <t>USD 34.00 - 35.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/7eed7ccb66a94d5f94b83cfb9b5b08e0-conservation-policy-analyst-xerces-society-inc-portland</t>
+  </si>
+  <si>
+    <t>Content Attorney - Trusts &amp; Estates - REMOTE</t>
+  </si>
+  <si>
+    <t>University of California Los Angeles</t>
+  </si>
+  <si>
+    <t>Los Angeles, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/843858d28fd4433f9a792fd8236bc7e7-content-attorney-trusts-estates-remote-university-of-california-los-angeles-los-angeles</t>
+  </si>
+  <si>
     <t>Coordinador de Pequeños Animales en el Santuario Ambue Ari - Trabaja con Fauna Rescatada en la Selva Boliviana</t>
   </si>
   <si>
@@ -841,6 +1048,72 @@
     <t>https://www.idealist.org/en/nonprofit-job/f6abf37dee8543daa2ea296c2c3d6e3c-coordinador-de-pequenos-animales-en-el-santuario-ambue-ari-trabaja-con-fauna-rescatada-en-la-selva-boliviana-comunidad-inti-wara-yassi-ciwy-ascension-de-guarayos</t>
   </si>
   <si>
+    <t>Customer Service Representative and Office Support Associate (part-time)</t>
+  </si>
+  <si>
+    <t>Educational Perspectives, nfp</t>
+  </si>
+  <si>
+    <t>USD 19.00 - 21.00/hour</t>
+  </si>
+  <si>
+    <t>Education, International Relations, Immigrants Or Refugees</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5c4af19eadac44f683c9dfb3ec6eac7d-customer-service-representative-and-office-support-associate-part-time-educational-perspectives-nfp-chicago</t>
+  </si>
+  <si>
+    <t>Day Labor Center Coordinator</t>
+  </si>
+  <si>
+    <t>POMONA ECONOMIC OPPORTUNITY CENTER</t>
+  </si>
+  <si>
+    <t>Pomona, California</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 29.00/hour</t>
+  </si>
+  <si>
+    <t>Economic Development, Immigrants Or Refugees, Job Workplace</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34d189f6daa94de783c87b427e6b9534-day-labor-center-coordinator-pomona-economic-opportunity-center-pomona</t>
+  </si>
+  <si>
+    <t>Development &amp; Donor Engagement Manager</t>
+  </si>
+  <si>
+    <t>Voices for Progress</t>
+  </si>
+  <si>
+    <t>USD 70000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Climate Change, Philanthropy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c22637cd3ab9438f8c5d55d518d2d8ef-development-donor-engagement-manager-voices-for-progress-washington</t>
+  </si>
+  <si>
+    <t>Development and Communications Coordinator</t>
+  </si>
+  <si>
+    <t>Gould Farm (William J. Gould Associates)</t>
+  </si>
+  <si>
+    <t>Monterey, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 45000.00 - 54000.00/year</t>
+  </si>
+  <si>
+    <t>Agriculture, Animals, Community Development</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c52b773cfa574360b41c608b9540990b-development-and-communications-coordinator-gould-farm-william-j-gould-associates-monterey</t>
+  </si>
+  <si>
     <t>Development Associate</t>
   </si>
   <si>
@@ -880,6 +1153,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/a15f85d236574572b49be40ba248006e-development-director-grant-writer-we-all-really-matter-inc-new-york</t>
   </si>
   <si>
+    <t>Digital Marketing &amp; Communications Manager</t>
+  </si>
+  <si>
+    <t>Greater DC Diaper Bank</t>
+  </si>
+  <si>
+    <t>Silver Spring, Maryland</t>
+  </si>
+  <si>
+    <t>Family, Health Medicine, Poverty</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f076a97a1e0640e99c07ef326070fb39-digital-marketing-communications-manager-greater-dc-diaper-bank-silver-spring</t>
+  </si>
+  <si>
+    <t>Director of Advancement</t>
+  </si>
+  <si>
+    <t>Farm and Wilderness Foundation</t>
+  </si>
+  <si>
+    <t>Plymouth, Vermont</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3c61e889bf904285af4cbfeddf19aa2b-director-of-advancement-farm-and-wilderness-foundation-plymouth</t>
+  </si>
+  <si>
+    <t>Director of Civic Engagement</t>
+  </si>
+  <si>
+    <t>The New York Immigration Coalition</t>
+  </si>
+  <si>
+    <t>USD 98400.00 - 98400.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Community Development, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/1e1de42e75dd4fc2b511a5e524dc5a85-director-of-civic-engagement-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
     <t>Director of Development</t>
   </si>
   <si>
@@ -898,6 +1219,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/9678fc4ee0e14b08a61188a3985e31de-director-of-development-the-salvation-army-of-broward-county-fort-lauderdale</t>
   </si>
   <si>
+    <t>League of Women Voters of Washington</t>
+  </si>
+  <si>
+    <t>Remote (Washington)</t>
+  </si>
+  <si>
+    <t>USD 39000.00 - 46000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Education, Human Rights Civil Liberties</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3520a3979b8b45e78b8406a1a02d18fc-director-of-development-league-of-women-voters-of-washington-seattle</t>
+  </si>
+  <si>
+    <t>Montreal Jewish Museum - Musée juif de Montréal</t>
+  </si>
+  <si>
+    <t>Montréal, Québec, CA</t>
+  </si>
+  <si>
+    <t>CAD 80000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/69f546a513864ac19d60493b02d50860-director-of-development-montreal-jewish-museum-musee-juif-de-montreal-montreal</t>
+  </si>
+  <si>
+    <t>Careers In Nonprofits, Inc.</t>
+  </si>
+  <si>
+    <t>Sonoma, California</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 135000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/4f629e67ddd84dfbb4af809cadd8bace-director-of-development-careers-in-nonprofits-inc-sonoma</t>
+  </si>
+  <si>
+    <t>Director of District Affairs, Office of Senator Bill Ferguson, Maryland Senate District 46</t>
+  </si>
+  <si>
+    <t>Maryland General Assembly, Office of the Senate President</t>
+  </si>
+  <si>
+    <t>Baltimore, Maryland</t>
+  </si>
+  <si>
+    <t>USD 75000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/government-job/f7e5c6e5e2cc42469747a5b3dc52a7b3-director-of-district-affairs-office-of-senator-bill-ferguson-maryland-senate-district-46-maryland-general-assembly-office-of-the-senate-president-baltimore</t>
+  </si>
+  <si>
     <t>Director of Family and Community Programs</t>
   </si>
   <si>
@@ -916,18 +1297,75 @@
     <t>https://www.idealist.org/en/nonprofit-job/7e96be8c09ff4501b7b90431f0a0d04f-director-of-family-and-community-programs-family-nurturing-center-of-ma-dorchester</t>
   </si>
   <si>
+    <t>Director of Finance</t>
+  </si>
+  <si>
+    <t>Boston Arts Academy Foundation</t>
+  </si>
+  <si>
+    <t>Boston, Massachusetts</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 110000.00/year</t>
+  </si>
+  <si>
+    <t>Arts Music, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/61509aeaee3a42a693ff6bc305e66176-director-of-finance-boston-arts-academy-foundation-boston</t>
+  </si>
+  <si>
     <t>Director of Financial and Administration</t>
   </si>
   <si>
-    <t>Careers In Nonprofits, Inc.</t>
-  </si>
-  <si>
     <t>USD 42.00 - 44.00/hour</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/job/1a14f8bdf5f84a2699f22cc2304020c0-director-of-financial-and-administration-careers-in-nonprofits-inc-chicago</t>
   </si>
   <si>
+    <t>Director of Grants &amp; Institutional Partnerships</t>
+  </si>
+  <si>
+    <t>ReSurge International</t>
+  </si>
+  <si>
+    <t>Remote</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 120000.00/year</t>
+  </si>
+  <si>
+    <t>Health Medicine, Philanthropy, International Relations</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fc23f43e53ad42f592e370e211e9c0bd-director-of-grants-institutional-partnerships-resurge-international-sunnyvale</t>
+  </si>
+  <si>
+    <t>Director of Impact and Data</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 80000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8cf67761567c4e958cae59351faa2a9a-director-of-impact-and-data-platform-for-social-impact-san-juan</t>
+  </si>
+  <si>
+    <t>Director of Marketing and Communications</t>
+  </si>
+  <si>
+    <t>Women Moving Millions, Inc.</t>
+  </si>
+  <si>
+    <t>USD 115000.00 - 140000.00/year</t>
+  </si>
+  <si>
+    <t>Philanthropy, Women</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/917d09d6a81b48ed8a23180e4fda98ca-director-of-marketing-and-communications-women-moving-millions-inc-new-york-city</t>
+  </si>
+  <si>
     <t>Director of Operations</t>
   </si>
   <si>
@@ -946,6 +1384,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/c19583c68f9f4fd4abd8b197fc30cefb-director-of-operations-thrive-for-longevity-west-palm-beach</t>
   </si>
   <si>
+    <t>Brain Rehabilitation and Injury Network</t>
+  </si>
+  <si>
+    <t>Cypress, California</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Education, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/02870bc1e0324da4a64a2b4189625625-director-of-operations-brain-rehabilitation-and-injury-network-cypress</t>
+  </si>
+  <si>
     <t>Director of Parenting Education and Training</t>
   </si>
   <si>
@@ -955,6 +1408,90 @@
     <t>https://www.idealist.org/en/nonprofit-job/271e56b4b017445cb8d12f1faca4afd0-director-of-parenting-education-and-training-family-nurturing-center-of-ma-dorchester</t>
   </si>
   <si>
+    <t>Director of Programs and Delivery</t>
+  </si>
+  <si>
+    <t>Jeweld Consulting</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 130000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/06ab671f8dba44e39528864cd64329d9-director-of-programs-and-delivery-jeweld-consulting-oakland</t>
+  </si>
+  <si>
+    <t>Domestic Violence Advocacy Manager</t>
+  </si>
+  <si>
+    <t>AACI- San Jose, California</t>
+  </si>
+  <si>
+    <t>San Jose, California</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 82000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Family, Health Medicine</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/29402041e02c485fa3ea76d1ecaff4d7-domestic-violence-advocacy-manager-aaci-san-jose-california-san-jose</t>
+  </si>
+  <si>
+    <t>Domestic Violence Hotline Counselor (On-Call)</t>
+  </si>
+  <si>
+    <t>Lutheran Settlement House</t>
+  </si>
+  <si>
+    <t>USD 17.00 - 18.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Housing Homelessness, Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f4a3074944e949249971d1cc7dc0f346-domestic-violence-hotline-counselor-on-call-lutheran-settlement-house-philadelphia</t>
+  </si>
+  <si>
+    <t>Domestic Violence Hotline Counselor/Advocate (part-time)</t>
+  </si>
+  <si>
+    <t>USD 18.00 - 20.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/230d1896dcf74ba0b121925458dcfc9a-domestic-violence-hotline-counseloradvocate-part-time-lutheran-settlement-house-philadelphia</t>
+  </si>
+  <si>
+    <t>Donor Engagement Officer</t>
+  </si>
+  <si>
+    <t>Food Lifeline</t>
+  </si>
+  <si>
+    <t>Seattle, WA</t>
+  </si>
+  <si>
+    <t>USD 80000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Hunger Food Security</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7264bd0560f243989de26da04a0f11ed-donor-engagement-officer-food-lifeline-seattle</t>
+  </si>
+  <si>
+    <t>ECM Case Manager</t>
+  </si>
+  <si>
+    <t>USD 25.00 - 28.50/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/34206896854e4b2f9a08c33d42a5c1a9-ecm-case-manager-aaci-san-jose-california-san-jose</t>
+  </si>
+  <si>
     <t>Educational Consultant – Remote (Commission-based)</t>
   </si>
   <si>
@@ -976,6 +1513,9 @@
     <t>https://www.idealist.org/en/nonprofit-job/3b046c85c40d49b0b5a7804b8383964a-educational-consultant-remote-commission-based-shivas-tutorial-hyderabad</t>
   </si>
   <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c74b4305d8834bb0b64955e9fa24642b-educational-consultant-remote-commission-based-shivas-tutorial-hyderabad</t>
+  </si>
+  <si>
     <t>Environmental Educator - KIDS for the BAY</t>
   </si>
   <si>
@@ -994,6 +1534,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/2a2ee94234ef4963af93decf4a1f22a2-environmental-educator-kids-for-the-bay-kids-for-the-bay-berkeley</t>
   </si>
   <si>
+    <t>ET Admin Manager + Secretary</t>
+  </si>
+  <si>
+    <t>Empower Tamizhagam</t>
+  </si>
+  <si>
+    <t>Chennai, Tamil Nadu, IN</t>
+  </si>
+  <si>
+    <t>Economic Development, Community Development, Entrepreneurship</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/ffc768cc03b84f5dbe277cb3f921f2ae-et-admin-manager-secretary-empower-tamizhagam-chennai</t>
+  </si>
+  <si>
     <t>Executive Director</t>
   </si>
   <si>
@@ -1012,15 +1567,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/0a534848dc9d41da90ff15a45d51b614-executive-director-maynard-house-hanover</t>
   </si>
   <si>
+    <t>Go Play</t>
+  </si>
+  <si>
+    <t>USD 100000.00 - 100000.00/year</t>
+  </si>
+  <si>
+    <t>Job Workplace, Children Youth, Sports Recreation</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/21e0aaec75a845c9b09fa5b33e994b1e-executive-director-go-play-washington</t>
+  </si>
+  <si>
     <t>Expert season Fundraiser</t>
   </si>
   <si>
     <t>Swift Sports Organisation</t>
   </si>
   <si>
-    <t>Remote</t>
-  </si>
-  <si>
     <t>USD 50.00 - 100.00/month</t>
   </si>
   <si>
@@ -1030,6 +1594,63 @@
     <t>https://www.idealist.org/en/nonprofit-job/e85c1498a8f54a568cb986ea2198e464-expert-season-fundraiser-swift-sports-organisation-kampala</t>
   </si>
   <si>
+    <t>Family Advocate at Shelter</t>
+  </si>
+  <si>
+    <t>USD 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/99b92be9fa7643c2845641ba3da9c5db-family-advocate-at-shelter-lutheran-settlement-house-philadelphia</t>
+  </si>
+  <si>
+    <t>Family Support Specialist</t>
+  </si>
+  <si>
+    <t>Northwest Resource Associates</t>
+  </si>
+  <si>
+    <t>Wasilla, Alaska</t>
+  </si>
+  <si>
+    <t>USD 52000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/4cb4de7eb3454f579dcc0faa1566e98c-family-support-specialist-northwest-resource-associates-wasilla</t>
+  </si>
+  <si>
+    <t>Field Representative/Organizer - UNITE HERE Local 2</t>
+  </si>
+  <si>
+    <t>UNITE HERE!</t>
+  </si>
+  <si>
+    <t>San Francisco, California</t>
+  </si>
+  <si>
+    <t>USD 39.94 - 39.94/hour</t>
+  </si>
+  <si>
+    <t>Immigrants Or Refugees, Women, Civic Engagement</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b99871a62fea4df98c2b3875d30722bf-field-representativeorganizer-unite-here-local-2-unite-here-san-francisco</t>
+  </si>
+  <si>
+    <t>Finance &amp; Administration Manager</t>
+  </si>
+  <si>
+    <t>Animal Defenders International</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>Animals</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/7a2de270853c4dafbc733dc01919044d-finance-administration-manager-animal-defenders-international-los-angeles</t>
+  </si>
+  <si>
     <t>Finance Manager</t>
   </si>
   <si>
@@ -1045,6 +1666,66 @@
     <t>https://www.idealist.org/en/nonprofit-job/e4275a0828ee4fad9c4f1049ce30e587-finance-manager-equality-federation-portland</t>
   </si>
   <si>
+    <t>Fundraising Associate</t>
+  </si>
+  <si>
+    <t>Golden Gate National Parks Conservancy</t>
+  </si>
+  <si>
+    <t>USD 32.00 - 32.00/hour</t>
+  </si>
+  <si>
+    <t>Environment, Philanthropy, Children Youth</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/08f20f40f04140838c4625f394acd70b-fundraising-associate-golden-gate-national-parks-conservancy-san-francisco</t>
+  </si>
+  <si>
+    <t>Fundraising Event Manager</t>
+  </si>
+  <si>
+    <t>Sarcoma Foundation of America</t>
+  </si>
+  <si>
+    <t>Bethesda, Maryland</t>
+  </si>
+  <si>
+    <t>Health Medicine, Education, Policy</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e885f508b8cd425cbcacb43a4e5a4025-fundraising-event-manager-sarcoma-foundation-of-america-bethesda</t>
+  </si>
+  <si>
+    <t>Gift Administration Associate</t>
+  </si>
+  <si>
+    <t>Environment, Children Youth, Climate Change</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3e9697d046b24e348095f4c6f221ca66-gift-administration-associate-golden-gate-national-parks-conservancy-san-francisco</t>
+  </si>
+  <si>
+    <t>Government Contracts Billing Specialist (Part-Time) - Spanish/English</t>
+  </si>
+  <si>
+    <t>USD 35000.00 - 40000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/f6ace9564b6a44f48fe8497951c072f0-government-contracts-billing-specialist-part-time-spanishenglish-anthos-home-new-york</t>
+  </si>
+  <si>
+    <t>Grants Assistant</t>
+  </si>
+  <si>
+    <t>Connecticut Humanities</t>
+  </si>
+  <si>
+    <t>Middletown, CT</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/86deb837d4934d88bcc8d3159bdf1294-grants-assistant-connecticut-humanities-middletown</t>
+  </si>
+  <si>
     <t>Grants Manager</t>
   </si>
   <si>
@@ -1069,6 +1750,39 @@
     <t>https://www.idealist.org/en/nonprofit-job/8218acb118504b9aaf488ad9d250a31e-groundskeeper-part-time-historic-hudson-valley-pocantico-hills</t>
   </si>
   <si>
+    <t>Interim Senior Program Manager, NYC Community Interpreter Bank</t>
+  </si>
+  <si>
+    <t>USD 81000.00 - 81000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/faac0ac6567f4eaba3f3b0bf4bb4c6cb-interim-senior-program-manager-nyc-community-interpreter-bank-the-new-york-immigration-coalition-new-york</t>
+  </si>
+  <si>
+    <t>IT Specialist</t>
+  </si>
+  <si>
+    <t>USD 40000.00 - 45000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/cce9a321af2d4c24b04085bb90948550-it-specialist-platform-for-social-impact-san-juan</t>
+  </si>
+  <si>
+    <t>Legal Assistance Intake Coordinator</t>
+  </si>
+  <si>
+    <t>1199SEIU Funds</t>
+  </si>
+  <si>
+    <t>USD 57800.00 - 72300.00/year</t>
+  </si>
+  <si>
+    <t>Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2a9740b34b144878889b5da14a0a1c8d-legal-assistance-intake-coordinator-1199seiu-funds-new-york</t>
+  </si>
+  <si>
     <t>Licensed Clinician-Worcester</t>
   </si>
   <si>
@@ -1102,6 +1816,69 @@
     <t>https://www.idealist.org/en/nonprofit-job/2df3d781b089492d8d1732bc0efe2766-literacy-interventionist-part-time-hopewell-inc-dedham</t>
   </si>
   <si>
+    <t>Major Gifts and Legacy Giving Officer</t>
+  </si>
+  <si>
+    <t>USD 90000.00 - 115000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/242146bb6fe6428dbb6e2ca9972e77db-major-gifts-and-legacy-giving-officer-food-lifeline-seattle</t>
+  </si>
+  <si>
+    <t>Manager of Program Operations and Community Support</t>
+  </si>
+  <si>
+    <t>Girls Who Code</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 87000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3ebd68d5139b49a8be9086ad6fd2a828-manager-of-program-operations-and-community-support-girls-who-code-new-york</t>
+  </si>
+  <si>
+    <t>Manager, Foundation Relations and Grants</t>
+  </si>
+  <si>
+    <t>Spence-Chapin Services to Families and Children</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e92605302b644e8298044e8d9ee05800-manager-foundation-relations-and-grants-spence-chapin-services-to-families-and-children-new-york</t>
+  </si>
+  <si>
+    <t>Managing Research Scientist, CVD</t>
+  </si>
+  <si>
+    <t>The Institute for Health Metrics and Evaluation</t>
+  </si>
+  <si>
+    <t>USD 120000.00 - 143820.00/year</t>
+  </si>
+  <si>
+    <t>Education, Health Medicine, Research Social Science</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/54476c23a83b4e8eae821946c7c45d7f-managing-research-scientist-cvd-the-institute-for-health-metrics-and-evaluation-seattle</t>
+  </si>
+  <si>
+    <t>Marketing Manager</t>
+  </si>
+  <si>
+    <t>ThinkGive, Inc.</t>
+  </si>
+  <si>
+    <t>Remote (Massachusetts)</t>
+  </si>
+  <si>
+    <t>USD 31000.00 - 36000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/2b723e5f7fb04985a175ffffb12a0431-marketing-manager-thinkgive-inc-concord</t>
+  </si>
+  <si>
     <t>MST Family Therapist</t>
   </si>
   <si>
@@ -1171,6 +1948,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/869bb6ce894f459dbf81a55d571b1b61-office-meeting-coordinator-bellarmine-jesuit-retreat-house-barrington</t>
   </si>
   <si>
+    <t>Office Operations Assistant</t>
+  </si>
+  <si>
+    <t>Wildlife Conservation Network</t>
+  </si>
+  <si>
+    <t>USD 33.00 - 36.00/hour</t>
+  </si>
+  <si>
+    <t>Animals, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/0c117fb8ab6d471293ee590580ff10b9-office-operations-assistant-wildlife-conservation-network-san-francisco</t>
+  </si>
+  <si>
     <t>OMRI is Hiring for a Bilingual Content Coordinator</t>
   </si>
   <si>
@@ -1186,12 +1978,114 @@
     <t>https://www.idealist.org/en/nonprofit-job/c37fab73ef1e4f239c9d881fc34304d3-omri-is-hiring-for-a-bilingual-content-coordinator-organic-materials-review-institute-omri-eugene</t>
   </si>
   <si>
+    <t>Operations Assistant</t>
+  </si>
+  <si>
+    <t>Osher Lifelong Learning Institute at American University</t>
+  </si>
+  <si>
+    <t>USD 55000.00 - 58000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6fb8755139fd497e970d42a768453a0a-operations-assistant-osher-lifelong-learning-institute-at-american-university-washington</t>
+  </si>
+  <si>
+    <t>Outdoor Education Program Coordinator</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>USD 30.00/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Community Development, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5530e63dd80e4c6fa40b8f3db0e80e7b-outdoor-education-program-coordinator-post-seattle</t>
+  </si>
+  <si>
+    <t>Part Time Volunteer Coordinator (LA/SGV) - AA4EF</t>
+  </si>
+  <si>
+    <t>The Chinese Progressive Association</t>
+  </si>
+  <si>
+    <t>San Gabriel, California</t>
+  </si>
+  <si>
+    <t>USD 26.00 - 26.00/hour</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/c7425e4c99154b449d9d998a4b0a5fd5-part-time-volunteer-coordinator-lasgv-aa4ef-the-chinese-progressive-association-san-gabriel</t>
+  </si>
+  <si>
+    <t>Part Time Volunteer Coordinator (Sacramento) - AA4EF</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/403bdebd82fa4963a174397d6d61f51e-part-time-volunteer-coordinator-sacramento-aa4ef-the-chinese-progressive-association-sacramento</t>
+  </si>
+  <si>
+    <t>Part-Time Civic Engagement Volunteer Coordinator - SBYC</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/6584a7baaded4275a4bdd8fa5c49acf7-part-time-civic-engagement-volunteer-coordinator-sbyc-the-chinese-progressive-association-san-jose</t>
+  </si>
+  <si>
     <t>Principal Paralegal</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/3adb3dfef8dc40b6b990d35907b9f19c-principal-paralegal-the-wright-center-for-community-health-and-graduate-medical-education-scranton</t>
   </si>
   <si>
+    <t>Program and Operations Coordinator</t>
+  </si>
+  <si>
+    <t>Scholarship Plus</t>
+  </si>
+  <si>
+    <t>Remote (New York)</t>
+  </si>
+  <si>
+    <t>Children Youth, Education, Mental Health</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/67704557db57414ab29daea4b2b20a25-program-and-operations-coordinator-scholarship-plus-new-york</t>
+  </si>
+  <si>
+    <t>Program Coordinator- Albany, NY</t>
+  </si>
+  <si>
+    <t>Albany, New York</t>
+  </si>
+  <si>
+    <t>USD 70000.00 - 75000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/job/f02f90d675e34705b87030079d3b2227-program-coordinator-albany-ny-the-research-foundation-for-suny-albany</t>
+  </si>
+  <si>
+    <t>Program Coordinator, Outreach</t>
+  </si>
+  <si>
+    <t>Trinity Church NYC</t>
+  </si>
+  <si>
+    <t>USD 78600.00 - 89500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/18f7f926f77d47c58615bdc32c562298-program-coordinator-outreach-trinity-church-nyc-new-york</t>
+  </si>
+  <si>
+    <t>Program Officer – Caring Community</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/5549e20c8e564f5993bd84eb3275af9c-program-officer-caring-community-platform-for-social-impact-san-juan</t>
+  </si>
+  <si>
     <t>Programs Officer, Scholars Programs</t>
   </si>
   <si>
@@ -1255,6 +2149,24 @@
     <t>https://www.idealist.org/en/nonprofit-job/67d45d2faf0a4fe3964f693b54832740-research-and-monitoring-officer-nature-foundation-sint-maarten-cole-bay</t>
   </si>
   <si>
+    <t>School Principal - Special Education</t>
+  </si>
+  <si>
+    <t>Villa Esperanza Services</t>
+  </si>
+  <si>
+    <t>Pasadena, California</t>
+  </si>
+  <si>
+    <t>USD 95000.00 - 118000.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Disability, Education</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/e5f35d02864b45c0b596ecd64f592a74-school-principal-special-education-villa-esperanza-services-pasadena</t>
+  </si>
+  <si>
     <t>Senior Attorney-Matrimonial Unit</t>
   </si>
   <si>
@@ -1285,6 +2197,30 @@
     <t>https://www.idealist.org/en/job/12ed664dfc51449599156beca02be170-senior-director-of-communications-shalom-hartman-institute-new-york</t>
   </si>
   <si>
+    <t>Senior Director, Development and Advancement</t>
+  </si>
+  <si>
+    <t>USD 140000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/3251df4af83d4321aef9338286835b4e-senior-director-development-and-advancement-spence-chapin-services-to-families-and-children-new-york</t>
+  </si>
+  <si>
+    <t>Senior Director, Digital Marketing</t>
+  </si>
+  <si>
+    <t>Brady United Against Gun Violence</t>
+  </si>
+  <si>
+    <t>USD 132000.00 - 150000.00/year</t>
+  </si>
+  <si>
+    <t>Civic Engagement, Conflict Resolution, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/16bca1ed284e444ea3a45b3b333605d5-senior-director-digital-marketing-brady-united-against-gun-violence-washington</t>
+  </si>
+  <si>
     <t>Senior Fundraising Manager (fully remote)</t>
   </si>
   <si>
@@ -1300,6 +2236,54 @@
     <t>https://www.idealist.org/en/nonprofit-job/b3181d5b1ccc4418a02561598be09313-senior-fundraising-manager-fully-remote-new-left-accelerator-san-francisco</t>
   </si>
   <si>
+    <t>Senior Housing Paralegal</t>
+  </si>
+  <si>
+    <t>Community Justice Project, Inc.</t>
+  </si>
+  <si>
+    <t>Miami, Florida</t>
+  </si>
+  <si>
+    <t>Human Rights Civil Liberties, Legal Assistance, Race Ethnicity</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b620522c9ab44559806ec77bf8360c46-senior-housing-paralegal-community-justice-project-inc-miami</t>
+  </si>
+  <si>
+    <t>Senior Manager, Emerging Programs</t>
+  </si>
+  <si>
+    <t>Shatterproof</t>
+  </si>
+  <si>
+    <t>USD 75000.00 - 85000.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Substance Abuse Addiction</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/27c6f25790ea4699904dbf3f54d56baa-senior-manager-emerging-programs-shatterproof-norwalk</t>
+  </si>
+  <si>
+    <t>Senior Program Manager, Climate Careers Bay Area</t>
+  </si>
+  <si>
+    <t>Rising Sun Center for Opportunity</t>
+  </si>
+  <si>
+    <t>Emeryville, California</t>
+  </si>
+  <si>
+    <t>USD 89100.00 - 93555.00/year</t>
+  </si>
+  <si>
+    <t>Children Youth, Energy, Environment</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/03dfea3340514bffb7f01b35a25f51d6-senior-program-manager-climate-careers-bay-area-rising-sun-center-for-opportunity-emeryville</t>
+  </si>
+  <si>
     <t>Service Enriched Housing Super Hero</t>
   </si>
   <si>
@@ -1348,9 +2332,6 @@
     <t>Civic Ventures</t>
   </si>
   <si>
-    <t>Seattle, Washington</t>
-  </si>
-  <si>
     <t>USD 85000.00 - 110000.00/year</t>
   </si>
   <si>
@@ -1360,6 +2341,21 @@
     <t>https://www.idealist.org/en/business-job/b7c2c916792844ef986ea52958708e47-social-media-content-manager-civic-ventures-seattle</t>
   </si>
   <si>
+    <t>Sr. Human Resources Partner</t>
+  </si>
+  <si>
+    <t>Disability Rights California</t>
+  </si>
+  <si>
+    <t>USD 82020.00 - 98817.00/year</t>
+  </si>
+  <si>
+    <t>Disability, Human Rights Civil Liberties, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/a1939afc9a1043549083c39b17141577-sr-human-resources-partner-disability-rights-california-los-angeles</t>
+  </si>
+  <si>
     <t>Staff Attorney</t>
   </si>
   <si>
@@ -1378,6 +2374,42 @@
     <t>https://www.idealist.org/en/nonprofit-job/7850e64733824a24a2db122e5ce1e973-staff-attorney-the-waterfront-project-inc-jersey-city</t>
   </si>
   <si>
+    <t>Housing Conservation Coordinators, Inc.</t>
+  </si>
+  <si>
+    <t>USD 78869.00 - 134389.00/year</t>
+  </si>
+  <si>
+    <t>Community Development, Family, Housing Homelessness</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d4cfa91bc33a48ca95b7e734ab211381-staff-attorney-housing-conservation-coordinators-inc-new-york</t>
+  </si>
+  <si>
+    <t>Staff Attorney - Eviction Defense</t>
+  </si>
+  <si>
+    <t>USD 65000.00 - 72500.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/d2eb04ef7e5343ad8590f02f17483feb-staff-attorney-eviction-defense-community-justice-project-inc-miami</t>
+  </si>
+  <si>
+    <t>Staff Attorney Tenants' Rights- Contra Costa County</t>
+  </si>
+  <si>
+    <t>Centro Legal de la Raza</t>
+  </si>
+  <si>
+    <t>USD 75321.00 - 89731.00/year</t>
+  </si>
+  <si>
+    <t>Housing Homelessness, Legal Assistance</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/b60077d4423f4a3fb9187593dd6dd68e-staff-attorney-tenants-rights-contra-costa-county-centro-legal-de-la-raza-oakland</t>
+  </si>
+  <si>
     <t>Staff Attorney-Housing Unit</t>
   </si>
   <si>
@@ -1399,6 +2431,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/fabbe8f2b3f44655ad81b03fe0ddf3bb-staff-attorney-mels-matrimonial-unit-district-council-37-health-security-plan-new-york</t>
   </si>
   <si>
+    <t>STAY FLY Program Lead Coach</t>
+  </si>
+  <si>
+    <t>Fresh Lifelines for Youth</t>
+  </si>
+  <si>
+    <t>USD 30.15 - 30.15/hour</t>
+  </si>
+  <si>
+    <t>Children Youth, Civic Engagement, Crime Safety</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8cb1aaa0916349bcbd5c7c15d9832e41-stay-fly-program-lead-coach-fresh-lifelines-for-youth-oakland</t>
+  </si>
+  <si>
     <t>Steve Lagerstrom</t>
   </si>
   <si>
@@ -1414,6 +2461,21 @@
     <t>https://www.idealist.org/en/nonprofit-job/583738eea22d46bcbea50177767eaad7-steve-lagerstrom-the-battery-conservancy-new-york</t>
   </si>
   <si>
+    <t>Supervising Social Security Attorney</t>
+  </si>
+  <si>
+    <t>Uptown People's Law Center</t>
+  </si>
+  <si>
+    <t>Chicago, IL</t>
+  </si>
+  <si>
+    <t>USD 85000.00 - 95000.00/year</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/8d20af561d98491ebf8d130ecc70c205-supervising-social-security-attorney-uptown-peoples-law-center-chicago</t>
+  </si>
+  <si>
     <t>Team Leader - Hotlines</t>
   </si>
   <si>
@@ -1426,6 +2488,15 @@
     <t>https://www.idealist.org/en/nonprofit-job/3f52439cb9774c74b660af6c8f9cf2f4-team-leader-hotlines-safe-horizon-new-york</t>
   </si>
   <si>
+    <t>Temporary Staff Attorney</t>
+  </si>
+  <si>
+    <t>New York Legal Assistance Group (NYLAG)</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/nonprofit-job/fb899b58d6484963afa3fc58b120cffc-temporary-staff-attorney-new-york-legal-assistance-group-nylag-new-york</t>
+  </si>
+  <si>
     <t>TÉRMINOS DE REFERENCIA ENCUESTADOR(A): Ciudad Juárez, Chihuahua</t>
   </si>
   <si>
@@ -1450,18 +2521,27 @@
     <t>https://www.idealist.org/en/nonprofit-job/99b052d70ed74e36a6f9a063e884b6c8-trauma-counselor-swf-safe-horizon-staten-island</t>
   </si>
   <si>
+    <t>Voter Contact Field Director</t>
+  </si>
+  <si>
+    <t>Vote Blue</t>
+  </si>
+  <si>
+    <t>Henderson, Nevada</t>
+  </si>
+  <si>
+    <t>USD 1146.00 - 1500.00/week</t>
+  </si>
+  <si>
+    <t>https://www.idealist.org/en/consultant-job/cd705523c4f7401f8f724d875783881b-voter-contact-field-director-vote-blue-henderson</t>
+  </si>
+  <si>
     <t>Warehouse Operations Manager</t>
   </si>
   <si>
-    <t>Food Lifeline</t>
-  </si>
-  <si>
     <t>USD 34.00 - 46.00/hour</t>
   </si>
   <si>
-    <t>Hunger Food Security</t>
-  </si>
-  <si>
     <t>https://www.idealist.org/en/nonprofit-job/c726d95a92ad421d99fa6e1f42010498-warehouse-operations-manager-food-lifeline-seattle</t>
   </si>
   <si>
@@ -1472,9 +2552,6 @@
   </si>
   <si>
     <t>Mar del Plata, Provincia de Buenos Aires, AR</t>
-  </si>
-  <si>
-    <t>Children Youth, Family</t>
   </si>
   <si>
     <t>https://www.idealist.org/en/nonprofit-job/24d88beee0aa4c35b63b366a17a25c8d-zona-mar-del-plata-lider-de-equipo-de-captadoresas-de-fondos-f2f-aldeas-infantiles-sos-argentina-mar-del-plata</t>
@@ -2747,7 +3824,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H63"/>
+  <dimension ref="A1:H142"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -2866,79 +3943,79 @@
         <v>211</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D6" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E6" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="F6" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D7" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E7" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F7" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="E8" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="F8" t="s">
         <v>231</v>
@@ -2952,134 +4029,134 @@
         <v>233</v>
       </c>
       <c r="B9" t="s">
-        <v>210</v>
+        <v>234</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D9" t="s">
         <v>199</v>
       </c>
       <c r="E9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F9" t="s">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B10" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
         <v>199</v>
       </c>
       <c r="E10" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C11" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
         <v>199</v>
       </c>
       <c r="E11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F11" t="s">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B12" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C12" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D12" t="s">
         <v>199</v>
       </c>
       <c r="E12" t="s">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="F12" t="s">
-        <v>251</v>
+        <v>219</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C13" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D13" t="s">
         <v>199</v>
       </c>
       <c r="E13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F13" t="s">
-        <v>194</v>
+        <v>258</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D14" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E14" t="s">
-        <v>261</v>
+        <v>219</v>
       </c>
       <c r="F14" t="s">
-        <v>262</v>
+        <v>219</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>263</v>
@@ -3090,10 +4167,10 @@
         <v>264</v>
       </c>
       <c r="B15" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C15" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D15" t="s">
         <v>199</v>
@@ -3119,289 +4196,289 @@
         <v>271</v>
       </c>
       <c r="D16" t="s">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="E16" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F16" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B17" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="C17" t="s">
-        <v>222</v>
+        <v>277</v>
       </c>
       <c r="D17" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F17" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D18" t="s">
         <v>199</v>
       </c>
       <c r="E18" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F18" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C19" t="s">
-        <v>222</v>
+        <v>287</v>
       </c>
       <c r="D19" t="s">
         <v>199</v>
       </c>
       <c r="E19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F19" t="s">
-        <v>206</v>
+        <v>289</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B20" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C20" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D20" t="s">
         <v>199</v>
       </c>
       <c r="E20" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F20" t="s">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B21" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C21" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D21" t="s">
         <v>199</v>
       </c>
       <c r="E21" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F21" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B22" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C22" t="s">
-        <v>255</v>
+        <v>304</v>
       </c>
       <c r="D22" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="E22" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F22" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B23" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C23" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="D23" t="s">
         <v>199</v>
       </c>
       <c r="E23" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="F23" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B24" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="C24" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="D24" t="s">
         <v>199</v>
       </c>
       <c r="E24" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F24" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B25" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C25" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="D25" t="s">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="E25" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F25" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B26" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="C26" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="D26" t="s">
-        <v>229</v>
+        <v>199</v>
       </c>
       <c r="E26" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F26" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B27" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C27" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="D27" t="s">
         <v>199</v>
       </c>
       <c r="E27" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="F27" t="s">
-        <v>330</v>
+        <v>219</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B28" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C28" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D28" t="s">
-        <v>316</v>
+        <v>199</v>
       </c>
       <c r="E28" t="s">
-        <v>335</v>
+        <v>219</v>
       </c>
       <c r="F28" t="s">
-        <v>336</v>
+        <v>219</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>337</v>
@@ -3415,801 +4492,2618 @@
         <v>339</v>
       </c>
       <c r="C29" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D29" t="s">
         <v>199</v>
       </c>
       <c r="E29" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F29" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B30" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C30" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="D30" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E30" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F30" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B31" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C31" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="D31" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E31" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F31" t="s">
-        <v>206</v>
+        <v>353</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B32" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="C32" t="s">
-        <v>353</v>
+        <v>246</v>
       </c>
       <c r="D32" t="s">
         <v>199</v>
       </c>
       <c r="E32" t="s">
-        <v>329</v>
+        <v>357</v>
       </c>
       <c r="F32" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="B33" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="C33" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D33" t="s">
         <v>199</v>
       </c>
       <c r="E33" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="F33" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B34" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C34" t="s">
-        <v>353</v>
+        <v>256</v>
       </c>
       <c r="D34" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="E34" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="F34" t="s">
-        <v>354</v>
+        <v>248</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B35" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C35" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="D35" t="s">
         <v>199</v>
       </c>
       <c r="E35" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="F35" t="s">
-        <v>366</v>
+        <v>267</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B36" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C36" t="s">
-        <v>23</v>
+        <v>256</v>
       </c>
       <c r="D36" t="s">
         <v>199</v>
       </c>
       <c r="E36" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="F36" t="s">
-        <v>371</v>
+        <v>219</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B37" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C37" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="D37" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E37" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="F37" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="B38" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C38" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D38" t="s">
         <v>199</v>
       </c>
       <c r="E38" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="F38" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="B39" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="C39" t="s">
-        <v>334</v>
+        <v>256</v>
       </c>
       <c r="D39" t="s">
         <v>199</v>
       </c>
       <c r="E39" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F39" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>396</v>
       </c>
       <c r="C40" t="s">
-        <v>205</v>
+        <v>397</v>
       </c>
       <c r="D40" t="s">
         <v>199</v>
       </c>
       <c r="E40" t="s">
-        <v>206</v>
+        <v>398</v>
       </c>
       <c r="F40" t="s">
-        <v>207</v>
+        <v>399</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B41" t="s">
-        <v>190</v>
+        <v>401</v>
       </c>
       <c r="C41" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D41" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E41" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="F41" t="s">
-        <v>194</v>
+        <v>404</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B42" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C42" t="s">
-        <v>255</v>
+        <v>407</v>
       </c>
       <c r="D42" t="s">
         <v>199</v>
       </c>
       <c r="E42" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="F42" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B43" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="C43" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="D43" t="s">
         <v>199</v>
       </c>
       <c r="E43" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="F43" t="s">
-        <v>405</v>
+        <v>219</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="B44" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C44" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D44" t="s">
         <v>199</v>
       </c>
       <c r="E44" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="F44" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B45" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C45" t="s">
-        <v>222</v>
+        <v>423</v>
       </c>
       <c r="D45" t="s">
         <v>199</v>
       </c>
       <c r="E45" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="F45" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B46" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>429</v>
       </c>
       <c r="D46" t="s">
         <v>199</v>
       </c>
       <c r="E46" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="F46" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="C47" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="D47" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="E47" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="F47" t="s">
-        <v>426</v>
+        <v>219</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="C48" t="s">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="D48" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E48" t="s">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="F48" t="s">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>433</v>
+        <v>441</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="B49" t="s">
-        <v>429</v>
+        <v>319</v>
       </c>
       <c r="C49" t="s">
-        <v>430</v>
+        <v>320</v>
       </c>
       <c r="D49" t="s">
         <v>199</v>
       </c>
       <c r="E49" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="F49" t="s">
-        <v>435</v>
+        <v>322</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>436</v>
+        <v>444</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B50" t="s">
-        <v>352</v>
+        <v>446</v>
       </c>
       <c r="C50" t="s">
-        <v>353</v>
+        <v>438</v>
       </c>
       <c r="D50" t="s">
         <v>199</v>
       </c>
       <c r="E50" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F50" t="s">
-        <v>354</v>
+        <v>448</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>451</v>
       </c>
       <c r="C51" t="s">
-        <v>271</v>
+        <v>452</v>
       </c>
       <c r="D51" t="s">
         <v>199</v>
       </c>
       <c r="E51" t="s">
-        <v>272</v>
+        <v>453</v>
       </c>
       <c r="F51" t="s">
-        <v>273</v>
+        <v>454</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>441</v>
+        <v>455</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="B52" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C52" t="s">
-        <v>444</v>
+        <v>457</v>
       </c>
       <c r="D52" t="s">
         <v>199</v>
       </c>
       <c r="E52" t="s">
-        <v>445</v>
+        <v>458</v>
       </c>
       <c r="F52" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s">
-        <v>449</v>
+        <v>422</v>
       </c>
       <c r="C53" t="s">
-        <v>450</v>
+        <v>423</v>
       </c>
       <c r="D53" t="s">
         <v>199</v>
       </c>
       <c r="E53" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="F53" t="s">
-        <v>452</v>
+        <v>425</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="B54" t="s">
-        <v>414</v>
+        <v>465</v>
       </c>
       <c r="C54" t="s">
-        <v>222</v>
+        <v>293</v>
       </c>
       <c r="D54" t="s">
         <v>199</v>
       </c>
       <c r="E54" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="F54" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B55" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="C55" t="s">
-        <v>222</v>
+        <v>471</v>
       </c>
       <c r="D55" t="s">
         <v>199</v>
       </c>
       <c r="E55" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="F55" t="s">
-        <v>459</v>
+        <v>473</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>460</v>
+        <v>474</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>461</v>
+        <v>475</v>
       </c>
       <c r="B56" t="s">
-        <v>462</v>
+        <v>476</v>
       </c>
       <c r="C56" t="s">
-        <v>463</v>
+        <v>262</v>
       </c>
       <c r="D56" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E56" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="F56" t="s">
-        <v>206</v>
+        <v>478</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>465</v>
+        <v>479</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>466</v>
+        <v>480</v>
       </c>
       <c r="B57" t="s">
-        <v>259</v>
+        <v>476</v>
       </c>
       <c r="C57" t="s">
-        <v>222</v>
+        <v>262</v>
       </c>
       <c r="D57" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="E57" t="s">
-        <v>467</v>
+        <v>481</v>
       </c>
       <c r="F57" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B58" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="C58" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="D58" t="s">
-        <v>218</v>
+        <v>199</v>
       </c>
       <c r="E58" t="s">
-        <v>206</v>
+        <v>486</v>
       </c>
       <c r="F58" t="s">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>474</v>
+        <v>488</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="B59" t="s">
-        <v>259</v>
+        <v>470</v>
       </c>
       <c r="C59" t="s">
-        <v>265</v>
+        <v>471</v>
       </c>
       <c r="D59" t="s">
         <v>199</v>
       </c>
       <c r="E59" t="s">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="F59" t="s">
-        <v>267</v>
+        <v>473</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="B60" t="s">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="C60" t="s">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="D60" t="s">
-        <v>199</v>
+        <v>495</v>
       </c>
       <c r="E60" t="s">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="F60" t="s">
-        <v>481</v>
+        <v>497</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>482</v>
+        <v>498</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="C61" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="D61" t="s">
-        <v>218</v>
+        <v>495</v>
       </c>
       <c r="E61" t="s">
-        <v>206</v>
+        <v>496</v>
       </c>
       <c r="F61" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="B62" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="C62" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="D62" t="s">
-        <v>218</v>
+        <v>272</v>
       </c>
       <c r="E62" t="s">
-        <v>206</v>
+        <v>503</v>
       </c>
       <c r="F62" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="B63" t="s">
+        <v>507</v>
+      </c>
+      <c r="C63" t="s">
+        <v>508</v>
+      </c>
+      <c r="D63" t="s">
+        <v>199</v>
+      </c>
+      <c r="E63" t="s">
+        <v>219</v>
+      </c>
+      <c r="F63" t="s">
+        <v>509</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>511</v>
+      </c>
+      <c r="B64" t="s">
+        <v>512</v>
+      </c>
+      <c r="C64" t="s">
+        <v>513</v>
+      </c>
+      <c r="D64" t="s">
+        <v>199</v>
+      </c>
+      <c r="E64" t="s">
+        <v>514</v>
+      </c>
+      <c r="F64" t="s">
+        <v>515</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>511</v>
+      </c>
+      <c r="B65" t="s">
+        <v>517</v>
+      </c>
+      <c r="C65" t="s">
+        <v>246</v>
+      </c>
+      <c r="D65" t="s">
+        <v>199</v>
+      </c>
+      <c r="E65" t="s">
+        <v>518</v>
+      </c>
+      <c r="F65" t="s">
+        <v>519</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>521</v>
+      </c>
+      <c r="B66" t="s">
+        <v>522</v>
+      </c>
+      <c r="C66" t="s">
+        <v>438</v>
+      </c>
+      <c r="D66" t="s">
+        <v>495</v>
+      </c>
+      <c r="E66" t="s">
+        <v>523</v>
+      </c>
+      <c r="F66" t="s">
+        <v>524</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>526</v>
+      </c>
+      <c r="B67" t="s">
+        <v>476</v>
+      </c>
+      <c r="C67" t="s">
+        <v>262</v>
+      </c>
+      <c r="D67" t="s">
+        <v>199</v>
+      </c>
+      <c r="E67" t="s">
+        <v>527</v>
+      </c>
+      <c r="F67" t="s">
+        <v>478</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>529</v>
+      </c>
+      <c r="B68" t="s">
+        <v>530</v>
+      </c>
+      <c r="C68" t="s">
+        <v>531</v>
+      </c>
+      <c r="D68" t="s">
+        <v>199</v>
+      </c>
+      <c r="E68" t="s">
+        <v>532</v>
+      </c>
+      <c r="F68" t="s">
+        <v>219</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>534</v>
+      </c>
+      <c r="B69" t="s">
+        <v>535</v>
+      </c>
+      <c r="C69" t="s">
+        <v>536</v>
+      </c>
+      <c r="D69" t="s">
+        <v>199</v>
+      </c>
+      <c r="E69" t="s">
+        <v>537</v>
+      </c>
+      <c r="F69" t="s">
+        <v>538</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>540</v>
+      </c>
+      <c r="B70" t="s">
+        <v>541</v>
+      </c>
+      <c r="C70" t="s">
+        <v>336</v>
+      </c>
+      <c r="D70" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" t="s">
+        <v>542</v>
+      </c>
+      <c r="F70" t="s">
+        <v>543</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>545</v>
+      </c>
+      <c r="B71" t="s">
+        <v>546</v>
+      </c>
+      <c r="C71" t="s">
+        <v>438</v>
+      </c>
+      <c r="D71" t="s">
+        <v>199</v>
+      </c>
+      <c r="E71" t="s">
+        <v>547</v>
+      </c>
+      <c r="F71" t="s">
+        <v>548</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>550</v>
+      </c>
+      <c r="B72" t="s">
+        <v>551</v>
+      </c>
+      <c r="C72" t="s">
+        <v>536</v>
+      </c>
+      <c r="D72" t="s">
+        <v>199</v>
+      </c>
+      <c r="E72" t="s">
+        <v>552</v>
+      </c>
+      <c r="F72" t="s">
+        <v>553</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>555</v>
+      </c>
+      <c r="B73" t="s">
+        <v>556</v>
+      </c>
+      <c r="C73" t="s">
+        <v>557</v>
+      </c>
+      <c r="D73" t="s">
+        <v>199</v>
+      </c>
+      <c r="E73" t="s">
+        <v>542</v>
+      </c>
+      <c r="F73" t="s">
+        <v>558</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>560</v>
+      </c>
+      <c r="B74" t="s">
+        <v>551</v>
+      </c>
+      <c r="C74" t="s">
+        <v>536</v>
+      </c>
+      <c r="D74" t="s">
+        <v>199</v>
+      </c>
+      <c r="E74" t="s">
+        <v>552</v>
+      </c>
+      <c r="F74" t="s">
+        <v>561</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>563</v>
+      </c>
+      <c r="B75" t="s">
+        <v>255</v>
+      </c>
+      <c r="C75" t="s">
+        <v>256</v>
+      </c>
+      <c r="D75" t="s">
+        <v>199</v>
+      </c>
+      <c r="E75" t="s">
+        <v>564</v>
+      </c>
+      <c r="F75" t="s">
+        <v>258</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>566</v>
+      </c>
+      <c r="B76" t="s">
+        <v>567</v>
+      </c>
+      <c r="C76" t="s">
+        <v>568</v>
+      </c>
+      <c r="D76" t="s">
+        <v>199</v>
+      </c>
+      <c r="E76" t="s">
+        <v>321</v>
+      </c>
+      <c r="F76" t="s">
+        <v>219</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>570</v>
+      </c>
+      <c r="B77" t="s">
+        <v>546</v>
+      </c>
+      <c r="C77" t="s">
+        <v>438</v>
+      </c>
+      <c r="D77" t="s">
+        <v>199</v>
+      </c>
+      <c r="E77" t="s">
+        <v>571</v>
+      </c>
+      <c r="F77" t="s">
+        <v>548</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>573</v>
+      </c>
+      <c r="B78" t="s">
+        <v>574</v>
+      </c>
+      <c r="C78" t="s">
+        <v>575</v>
+      </c>
+      <c r="D78" t="s">
+        <v>212</v>
+      </c>
+      <c r="E78" t="s">
+        <v>576</v>
+      </c>
+      <c r="F78" t="s">
+        <v>219</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>578</v>
+      </c>
+      <c r="B79" t="s">
+        <v>391</v>
+      </c>
+      <c r="C79" t="s">
+        <v>256</v>
+      </c>
+      <c r="D79" t="s">
+        <v>272</v>
+      </c>
+      <c r="E79" t="s">
+        <v>579</v>
+      </c>
+      <c r="F79" t="s">
+        <v>393</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>581</v>
+      </c>
+      <c r="B80" t="s">
+        <v>319</v>
+      </c>
+      <c r="C80" t="s">
+        <v>320</v>
+      </c>
+      <c r="D80" t="s">
+        <v>199</v>
+      </c>
+      <c r="E80" t="s">
+        <v>582</v>
+      </c>
+      <c r="F80" t="s">
+        <v>322</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>584</v>
+      </c>
+      <c r="B81" t="s">
+        <v>585</v>
+      </c>
+      <c r="C81" t="s">
+        <v>256</v>
+      </c>
+      <c r="D81" t="s">
+        <v>199</v>
+      </c>
+      <c r="E81" t="s">
+        <v>586</v>
+      </c>
+      <c r="F81" t="s">
+        <v>587</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>589</v>
+      </c>
+      <c r="B82" t="s">
+        <v>590</v>
+      </c>
+      <c r="C82" t="s">
+        <v>591</v>
+      </c>
+      <c r="D82" t="s">
+        <v>199</v>
+      </c>
+      <c r="E82" t="s">
+        <v>514</v>
+      </c>
+      <c r="F82" t="s">
+        <v>592</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>594</v>
+      </c>
+      <c r="B83" t="s">
+        <v>590</v>
+      </c>
+      <c r="C83" t="s">
+        <v>591</v>
+      </c>
+      <c r="D83" t="s">
+        <v>199</v>
+      </c>
+      <c r="E83" t="s">
+        <v>595</v>
+      </c>
+      <c r="F83" t="s">
+        <v>592</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>597</v>
+      </c>
+      <c r="B84" t="s">
+        <v>590</v>
+      </c>
+      <c r="C84" t="s">
+        <v>591</v>
+      </c>
+      <c r="D84" t="s">
+        <v>212</v>
+      </c>
+      <c r="E84" t="s">
+        <v>598</v>
+      </c>
+      <c r="F84" t="s">
+        <v>592</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>600</v>
+      </c>
+      <c r="B85" t="s">
         <v>484</v>
       </c>
-      <c r="C63" t="s">
-        <v>492</v>
-      </c>
-      <c r="D63" t="s">
-        <v>218</v>
-      </c>
-      <c r="E63" t="s">
-        <v>206</v>
-      </c>
-      <c r="F63" t="s">
-        <v>486</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>493</v>
+      <c r="C85" t="s">
+        <v>287</v>
+      </c>
+      <c r="D85" t="s">
+        <v>199</v>
+      </c>
+      <c r="E85" t="s">
+        <v>601</v>
+      </c>
+      <c r="F85" t="s">
+        <v>487</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>603</v>
+      </c>
+      <c r="B86" t="s">
+        <v>604</v>
+      </c>
+      <c r="C86" t="s">
+        <v>256</v>
+      </c>
+      <c r="D86" t="s">
+        <v>199</v>
+      </c>
+      <c r="E86" t="s">
+        <v>605</v>
+      </c>
+      <c r="F86" t="s">
+        <v>606</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>608</v>
+      </c>
+      <c r="B87" t="s">
+        <v>609</v>
+      </c>
+      <c r="C87" t="s">
+        <v>256</v>
+      </c>
+      <c r="D87" t="s">
+        <v>199</v>
+      </c>
+      <c r="E87" t="s">
+        <v>443</v>
+      </c>
+      <c r="F87" t="s">
+        <v>289</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>611</v>
+      </c>
+      <c r="B88" t="s">
+        <v>612</v>
+      </c>
+      <c r="C88" t="s">
+        <v>438</v>
+      </c>
+      <c r="D88" t="s">
+        <v>199</v>
+      </c>
+      <c r="E88" t="s">
+        <v>613</v>
+      </c>
+      <c r="F88" t="s">
+        <v>614</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>616</v>
+      </c>
+      <c r="B89" t="s">
+        <v>617</v>
+      </c>
+      <c r="C89" t="s">
+        <v>618</v>
+      </c>
+      <c r="D89" t="s">
+        <v>212</v>
+      </c>
+      <c r="E89" t="s">
+        <v>619</v>
+      </c>
+      <c r="F89" t="s">
+        <v>267</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>621</v>
+      </c>
+      <c r="B90" t="s">
+        <v>622</v>
+      </c>
+      <c r="C90" t="s">
+        <v>623</v>
+      </c>
+      <c r="D90" t="s">
+        <v>199</v>
+      </c>
+      <c r="E90" t="s">
+        <v>624</v>
+      </c>
+      <c r="F90" t="s">
+        <v>625</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>627</v>
+      </c>
+      <c r="B91" t="s">
+        <v>628</v>
+      </c>
+      <c r="C91" t="s">
+        <v>23</v>
+      </c>
+      <c r="D91" t="s">
+        <v>199</v>
+      </c>
+      <c r="E91" t="s">
+        <v>629</v>
+      </c>
+      <c r="F91" t="s">
+        <v>630</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>632</v>
+      </c>
+      <c r="B92" t="s">
+        <v>633</v>
+      </c>
+      <c r="C92" t="s">
+        <v>634</v>
+      </c>
+      <c r="D92" t="s">
+        <v>212</v>
+      </c>
+      <c r="E92" t="s">
+        <v>635</v>
+      </c>
+      <c r="F92" t="s">
+        <v>636</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>638</v>
+      </c>
+      <c r="B93" t="s">
+        <v>639</v>
+      </c>
+      <c r="C93" t="s">
+        <v>640</v>
+      </c>
+      <c r="D93" t="s">
+        <v>199</v>
+      </c>
+      <c r="E93" t="s">
+        <v>641</v>
+      </c>
+      <c r="F93" t="s">
+        <v>642</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>644</v>
+      </c>
+      <c r="B94" t="s">
+        <v>645</v>
+      </c>
+      <c r="C94" t="s">
+        <v>536</v>
+      </c>
+      <c r="D94" t="s">
+        <v>199</v>
+      </c>
+      <c r="E94" t="s">
+        <v>646</v>
+      </c>
+      <c r="F94" t="s">
+        <v>647</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>649</v>
+      </c>
+      <c r="B95" t="s">
+        <v>650</v>
+      </c>
+      <c r="C95" t="s">
+        <v>438</v>
+      </c>
+      <c r="D95" t="s">
+        <v>199</v>
+      </c>
+      <c r="E95" t="s">
+        <v>651</v>
+      </c>
+      <c r="F95" t="s">
+        <v>652</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>654</v>
+      </c>
+      <c r="B96" t="s">
+        <v>655</v>
+      </c>
+      <c r="C96" t="s">
+        <v>246</v>
+      </c>
+      <c r="D96" t="s">
+        <v>199</v>
+      </c>
+      <c r="E96" t="s">
+        <v>656</v>
+      </c>
+      <c r="F96" t="s">
+        <v>219</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>658</v>
+      </c>
+      <c r="B97" t="s">
+        <v>659</v>
+      </c>
+      <c r="C97" t="s">
+        <v>287</v>
+      </c>
+      <c r="D97" t="s">
+        <v>212</v>
+      </c>
+      <c r="E97" t="s">
+        <v>660</v>
+      </c>
+      <c r="F97" t="s">
+        <v>661</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>663</v>
+      </c>
+      <c r="B98" t="s">
+        <v>664</v>
+      </c>
+      <c r="C98" t="s">
+        <v>665</v>
+      </c>
+      <c r="D98" t="s">
+        <v>192</v>
+      </c>
+      <c r="E98" t="s">
+        <v>666</v>
+      </c>
+      <c r="F98" t="s">
+        <v>219</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>668</v>
+      </c>
+      <c r="B99" t="s">
+        <v>664</v>
+      </c>
+      <c r="C99" t="s">
+        <v>669</v>
+      </c>
+      <c r="D99" t="s">
+        <v>192</v>
+      </c>
+      <c r="E99" t="s">
+        <v>666</v>
+      </c>
+      <c r="F99" t="s">
+        <v>219</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>671</v>
+      </c>
+      <c r="B100" t="s">
+        <v>664</v>
+      </c>
+      <c r="C100" t="s">
+        <v>471</v>
+      </c>
+      <c r="D100" t="s">
+        <v>192</v>
+      </c>
+      <c r="E100" t="s">
+        <v>666</v>
+      </c>
+      <c r="F100" t="s">
+        <v>219</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>673</v>
+      </c>
+      <c r="B101" t="s">
+        <v>229</v>
+      </c>
+      <c r="C101" t="s">
+        <v>230</v>
+      </c>
+      <c r="D101" t="s">
+        <v>199</v>
+      </c>
+      <c r="E101" t="s">
+        <v>219</v>
+      </c>
+      <c r="F101" t="s">
+        <v>231</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>675</v>
+      </c>
+      <c r="B102" t="s">
+        <v>676</v>
+      </c>
+      <c r="C102" t="s">
+        <v>677</v>
+      </c>
+      <c r="D102" t="s">
+        <v>199</v>
+      </c>
+      <c r="E102" t="s">
+        <v>257</v>
+      </c>
+      <c r="F102" t="s">
+        <v>678</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>680</v>
+      </c>
+      <c r="B103" t="s">
+        <v>251</v>
+      </c>
+      <c r="C103" t="s">
+        <v>681</v>
+      </c>
+      <c r="D103" t="s">
+        <v>199</v>
+      </c>
+      <c r="E103" t="s">
+        <v>682</v>
+      </c>
+      <c r="F103" t="s">
+        <v>219</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>684</v>
+      </c>
+      <c r="B104" t="s">
+        <v>685</v>
+      </c>
+      <c r="C104" t="s">
+        <v>256</v>
+      </c>
+      <c r="D104" t="s">
+        <v>199</v>
+      </c>
+      <c r="E104" t="s">
+        <v>686</v>
+      </c>
+      <c r="F104" t="s">
+        <v>219</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>688</v>
+      </c>
+      <c r="B105" t="s">
+        <v>319</v>
+      </c>
+      <c r="C105" t="s">
+        <v>320</v>
+      </c>
+      <c r="D105" t="s">
+        <v>199</v>
+      </c>
+      <c r="E105" t="s">
+        <v>582</v>
+      </c>
+      <c r="F105" t="s">
+        <v>322</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>690</v>
+      </c>
+      <c r="B106" t="s">
+        <v>190</v>
+      </c>
+      <c r="C106" t="s">
+        <v>691</v>
+      </c>
+      <c r="D106" t="s">
+        <v>199</v>
+      </c>
+      <c r="E106" t="s">
+        <v>692</v>
+      </c>
+      <c r="F106" t="s">
+        <v>194</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>694</v>
+      </c>
+      <c r="B107" t="s">
+        <v>695</v>
+      </c>
+      <c r="C107" t="s">
+        <v>304</v>
+      </c>
+      <c r="D107" t="s">
+        <v>199</v>
+      </c>
+      <c r="E107" t="s">
+        <v>696</v>
+      </c>
+      <c r="F107" t="s">
+        <v>697</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>699</v>
+      </c>
+      <c r="B108" t="s">
+        <v>700</v>
+      </c>
+      <c r="C108" t="s">
+        <v>701</v>
+      </c>
+      <c r="D108" t="s">
+        <v>199</v>
+      </c>
+      <c r="E108" t="s">
+        <v>702</v>
+      </c>
+      <c r="F108" t="s">
+        <v>703</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>705</v>
+      </c>
+      <c r="B109" t="s">
+        <v>706</v>
+      </c>
+      <c r="C109" t="s">
+        <v>707</v>
+      </c>
+      <c r="D109" t="s">
+        <v>199</v>
+      </c>
+      <c r="E109" t="s">
+        <v>708</v>
+      </c>
+      <c r="F109" t="s">
+        <v>709</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>711</v>
+      </c>
+      <c r="B110" t="s">
+        <v>712</v>
+      </c>
+      <c r="C110" t="s">
+        <v>713</v>
+      </c>
+      <c r="D110" t="s">
+        <v>199</v>
+      </c>
+      <c r="E110" t="s">
+        <v>714</v>
+      </c>
+      <c r="F110" t="s">
+        <v>715</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>717</v>
+      </c>
+      <c r="B111" t="s">
+        <v>718</v>
+      </c>
+      <c r="C111" t="s">
+        <v>256</v>
+      </c>
+      <c r="D111" t="s">
+        <v>199</v>
+      </c>
+      <c r="E111" t="s">
+        <v>719</v>
+      </c>
+      <c r="F111" t="s">
+        <v>720</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>722</v>
+      </c>
+      <c r="B112" t="s">
+        <v>723</v>
+      </c>
+      <c r="C112" t="s">
+        <v>256</v>
+      </c>
+      <c r="D112" t="s">
+        <v>199</v>
+      </c>
+      <c r="E112" t="s">
+        <v>724</v>
+      </c>
+      <c r="F112" t="s">
+        <v>725</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>727</v>
+      </c>
+      <c r="B113" t="s">
+        <v>609</v>
+      </c>
+      <c r="C113" t="s">
+        <v>256</v>
+      </c>
+      <c r="D113" t="s">
+        <v>199</v>
+      </c>
+      <c r="E113" t="s">
+        <v>728</v>
+      </c>
+      <c r="F113" t="s">
+        <v>289</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>730</v>
+      </c>
+      <c r="B114" t="s">
+        <v>731</v>
+      </c>
+      <c r="C114" t="s">
+        <v>246</v>
+      </c>
+      <c r="D114" t="s">
+        <v>199</v>
+      </c>
+      <c r="E114" t="s">
+        <v>732</v>
+      </c>
+      <c r="F114" t="s">
+        <v>733</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>735</v>
+      </c>
+      <c r="B115" t="s">
+        <v>736</v>
+      </c>
+      <c r="C115" t="s">
+        <v>438</v>
+      </c>
+      <c r="D115" t="s">
+        <v>212</v>
+      </c>
+      <c r="E115" t="s">
+        <v>737</v>
+      </c>
+      <c r="F115" t="s">
+        <v>738</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>740</v>
+      </c>
+      <c r="B116" t="s">
+        <v>741</v>
+      </c>
+      <c r="C116" t="s">
+        <v>742</v>
+      </c>
+      <c r="D116" t="s">
+        <v>199</v>
+      </c>
+      <c r="E116" t="s">
+        <v>357</v>
+      </c>
+      <c r="F116" t="s">
+        <v>743</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>745</v>
+      </c>
+      <c r="B117" t="s">
+        <v>746</v>
+      </c>
+      <c r="C117" t="s">
+        <v>438</v>
+      </c>
+      <c r="D117" t="s">
+        <v>199</v>
+      </c>
+      <c r="E117" t="s">
+        <v>747</v>
+      </c>
+      <c r="F117" t="s">
+        <v>748</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>750</v>
+      </c>
+      <c r="B118" t="s">
+        <v>751</v>
+      </c>
+      <c r="C118" t="s">
+        <v>752</v>
+      </c>
+      <c r="D118" t="s">
+        <v>199</v>
+      </c>
+      <c r="E118" t="s">
+        <v>753</v>
+      </c>
+      <c r="F118" t="s">
+        <v>754</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>756</v>
+      </c>
+      <c r="B119" t="s">
+        <v>757</v>
+      </c>
+      <c r="C119" t="s">
+        <v>758</v>
+      </c>
+      <c r="D119" t="s">
+        <v>212</v>
+      </c>
+      <c r="E119" t="s">
+        <v>759</v>
+      </c>
+      <c r="F119" t="s">
+        <v>760</v>
+      </c>
+      <c r="H119" s="2" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>756</v>
+      </c>
+      <c r="B120" t="s">
+        <v>757</v>
+      </c>
+      <c r="C120" t="s">
+        <v>758</v>
+      </c>
+      <c r="D120" t="s">
+        <v>199</v>
+      </c>
+      <c r="E120" t="s">
+        <v>762</v>
+      </c>
+      <c r="F120" t="s">
+        <v>763</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>765</v>
+      </c>
+      <c r="B121" t="s">
+        <v>590</v>
+      </c>
+      <c r="C121" t="s">
+        <v>591</v>
+      </c>
+      <c r="D121" t="s">
+        <v>199</v>
+      </c>
+      <c r="E121" t="s">
+        <v>766</v>
+      </c>
+      <c r="F121" t="s">
+        <v>592</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>768</v>
+      </c>
+      <c r="B122" t="s">
+        <v>339</v>
+      </c>
+      <c r="C122" t="s">
+        <v>340</v>
+      </c>
+      <c r="D122" t="s">
+        <v>199</v>
+      </c>
+      <c r="E122" t="s">
+        <v>341</v>
+      </c>
+      <c r="F122" t="s">
+        <v>342</v>
+      </c>
+      <c r="H122" s="2" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>770</v>
+      </c>
+      <c r="B123" t="s">
+        <v>771</v>
+      </c>
+      <c r="C123" t="s">
+        <v>287</v>
+      </c>
+      <c r="D123" t="s">
+        <v>199</v>
+      </c>
+      <c r="E123" t="s">
+        <v>772</v>
+      </c>
+      <c r="F123" t="s">
+        <v>773</v>
+      </c>
+      <c r="H123" s="2" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>775</v>
+      </c>
+      <c r="B124" t="s">
+        <v>776</v>
+      </c>
+      <c r="C124" t="s">
+        <v>336</v>
+      </c>
+      <c r="D124" t="s">
+        <v>199</v>
+      </c>
+      <c r="E124" t="s">
+        <v>777</v>
+      </c>
+      <c r="F124" t="s">
+        <v>778</v>
+      </c>
+      <c r="H124" s="2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>780</v>
+      </c>
+      <c r="B125" t="s">
+        <v>781</v>
+      </c>
+      <c r="C125" t="s">
+        <v>782</v>
+      </c>
+      <c r="D125" t="s">
+        <v>199</v>
+      </c>
+      <c r="E125" t="s">
+        <v>783</v>
+      </c>
+      <c r="F125" t="s">
+        <v>784</v>
+      </c>
+      <c r="H125" s="2" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>780</v>
+      </c>
+      <c r="B126" t="s">
+        <v>786</v>
+      </c>
+      <c r="C126" t="s">
+        <v>256</v>
+      </c>
+      <c r="D126" t="s">
+        <v>199</v>
+      </c>
+      <c r="E126" t="s">
+        <v>787</v>
+      </c>
+      <c r="F126" t="s">
+        <v>788</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>790</v>
+      </c>
+      <c r="B127" t="s">
+        <v>741</v>
+      </c>
+      <c r="C127" t="s">
+        <v>742</v>
+      </c>
+      <c r="D127" t="s">
+        <v>199</v>
+      </c>
+      <c r="E127" t="s">
+        <v>791</v>
+      </c>
+      <c r="F127" t="s">
+        <v>743</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>793</v>
+      </c>
+      <c r="B128" t="s">
+        <v>794</v>
+      </c>
+      <c r="C128" t="s">
+        <v>293</v>
+      </c>
+      <c r="D128" t="s">
+        <v>199</v>
+      </c>
+      <c r="E128" t="s">
+        <v>795</v>
+      </c>
+      <c r="F128" t="s">
+        <v>796</v>
+      </c>
+      <c r="H128" s="2" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>798</v>
+      </c>
+      <c r="B129" t="s">
+        <v>718</v>
+      </c>
+      <c r="C129" t="s">
+        <v>256</v>
+      </c>
+      <c r="D129" t="s">
+        <v>199</v>
+      </c>
+      <c r="E129" t="s">
+        <v>799</v>
+      </c>
+      <c r="F129" t="s">
+        <v>800</v>
+      </c>
+      <c r="H129" s="2" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>802</v>
+      </c>
+      <c r="B130" t="s">
+        <v>718</v>
+      </c>
+      <c r="C130" t="s">
+        <v>256</v>
+      </c>
+      <c r="D130" t="s">
+        <v>199</v>
+      </c>
+      <c r="E130" t="s">
+        <v>799</v>
+      </c>
+      <c r="F130" t="s">
+        <v>803</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>805</v>
+      </c>
+      <c r="B131" t="s">
+        <v>806</v>
+      </c>
+      <c r="C131" t="s">
+        <v>293</v>
+      </c>
+      <c r="D131" t="s">
+        <v>199</v>
+      </c>
+      <c r="E131" t="s">
+        <v>807</v>
+      </c>
+      <c r="F131" t="s">
+        <v>808</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>810</v>
+      </c>
+      <c r="B132" t="s">
+        <v>811</v>
+      </c>
+      <c r="C132" t="s">
+        <v>812</v>
+      </c>
+      <c r="D132" t="s">
+        <v>199</v>
+      </c>
+      <c r="E132" t="s">
+        <v>813</v>
+      </c>
+      <c r="F132" t="s">
+        <v>219</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>815</v>
+      </c>
+      <c r="B133" t="s">
+        <v>816</v>
+      </c>
+      <c r="C133" t="s">
+        <v>817</v>
+      </c>
+      <c r="D133" t="s">
+        <v>199</v>
+      </c>
+      <c r="E133" t="s">
+        <v>818</v>
+      </c>
+      <c r="F133" t="s">
+        <v>778</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>820</v>
+      </c>
+      <c r="B134" t="s">
+        <v>308</v>
+      </c>
+      <c r="C134" t="s">
+        <v>256</v>
+      </c>
+      <c r="D134" t="s">
+        <v>199</v>
+      </c>
+      <c r="E134" t="s">
+        <v>821</v>
+      </c>
+      <c r="F134" t="s">
+        <v>822</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>824</v>
+      </c>
+      <c r="B135" t="s">
+        <v>825</v>
+      </c>
+      <c r="C135" t="s">
+        <v>256</v>
+      </c>
+      <c r="D135" t="s">
+        <v>199</v>
+      </c>
+      <c r="E135" t="s">
+        <v>219</v>
+      </c>
+      <c r="F135" t="s">
+        <v>587</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>827</v>
+      </c>
+      <c r="B136" t="s">
+        <v>828</v>
+      </c>
+      <c r="C136" t="s">
+        <v>829</v>
+      </c>
+      <c r="D136" t="s">
+        <v>212</v>
+      </c>
+      <c r="E136" t="s">
+        <v>219</v>
+      </c>
+      <c r="F136" t="s">
+        <v>830</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>832</v>
+      </c>
+      <c r="B137" t="s">
+        <v>308</v>
+      </c>
+      <c r="C137" t="s">
+        <v>314</v>
+      </c>
+      <c r="D137" t="s">
+        <v>199</v>
+      </c>
+      <c r="E137" t="s">
+        <v>833</v>
+      </c>
+      <c r="F137" t="s">
+        <v>316</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>835</v>
+      </c>
+      <c r="B138" t="s">
+        <v>836</v>
+      </c>
+      <c r="C138" t="s">
+        <v>837</v>
+      </c>
+      <c r="D138" t="s">
+        <v>199</v>
+      </c>
+      <c r="E138" t="s">
+        <v>838</v>
+      </c>
+      <c r="F138" t="s">
+        <v>419</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>840</v>
+      </c>
+      <c r="B139" t="s">
+        <v>484</v>
+      </c>
+      <c r="C139" t="s">
+        <v>287</v>
+      </c>
+      <c r="D139" t="s">
+        <v>199</v>
+      </c>
+      <c r="E139" t="s">
+        <v>841</v>
+      </c>
+      <c r="F139" t="s">
+        <v>487</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>843</v>
+      </c>
+      <c r="B140" t="s">
+        <v>844</v>
+      </c>
+      <c r="C140" t="s">
+        <v>845</v>
+      </c>
+      <c r="D140" t="s">
+        <v>212</v>
+      </c>
+      <c r="E140" t="s">
+        <v>219</v>
+      </c>
+      <c r="F140" t="s">
+        <v>289</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>847</v>
+      </c>
+      <c r="B141" t="s">
+        <v>844</v>
+      </c>
+      <c r="C141" t="s">
+        <v>848</v>
+      </c>
+      <c r="D141" t="s">
+        <v>212</v>
+      </c>
+      <c r="E141" t="s">
+        <v>219</v>
+      </c>
+      <c r="F141" t="s">
+        <v>289</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>850</v>
+      </c>
+      <c r="B142" t="s">
+        <v>844</v>
+      </c>
+      <c r="C142" t="s">
+        <v>851</v>
+      </c>
+      <c r="D142" t="s">
+        <v>212</v>
+      </c>
+      <c r="E142" t="s">
+        <v>219</v>
+      </c>
+      <c r="F142" t="s">
+        <v>289</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>852</v>
       </c>
     </row>
   </sheetData>
@@ -4277,6 +7171,85 @@
     <hyperlink ref="H61" r:id="rId60"/>
     <hyperlink ref="H62" r:id="rId61"/>
     <hyperlink ref="H63" r:id="rId62"/>
+    <hyperlink ref="H64" r:id="rId63"/>
+    <hyperlink ref="H65" r:id="rId64"/>
+    <hyperlink ref="H66" r:id="rId65"/>
+    <hyperlink ref="H67" r:id="rId66"/>
+    <hyperlink ref="H68" r:id="rId67"/>
+    <hyperlink ref="H69" r:id="rId68"/>
+    <hyperlink ref="H70" r:id="rId69"/>
+    <hyperlink ref="H71" r:id="rId70"/>
+    <hyperlink ref="H72" r:id="rId71"/>
+    <hyperlink ref="H73" r:id="rId72"/>
+    <hyperlink ref="H74" r:id="rId73"/>
+    <hyperlink ref="H75" r:id="rId74"/>
+    <hyperlink ref="H76" r:id="rId75"/>
+    <hyperlink ref="H77" r:id="rId76"/>
+    <hyperlink ref="H78" r:id="rId77"/>
+    <hyperlink ref="H79" r:id="rId78"/>
+    <hyperlink ref="H80" r:id="rId79"/>
+    <hyperlink ref="H81" r:id="rId80"/>
+    <hyperlink ref="H82" r:id="rId81"/>
+    <hyperlink ref="H83" r:id="rId82"/>
+    <hyperlink ref="H84" r:id="rId83"/>
+    <hyperlink ref="H85" r:id="rId84"/>
+    <hyperlink ref="H86" r:id="rId85"/>
+    <hyperlink ref="H87" r:id="rId86"/>
+    <hyperlink ref="H88" r:id="rId87"/>
+    <hyperlink ref="H89" r:id="rId88"/>
+    <hyperlink ref="H90" r:id="rId89"/>
+    <hyperlink ref="H91" r:id="rId90"/>
+    <hyperlink ref="H92" r:id="rId91"/>
+    <hyperlink ref="H93" r:id="rId92"/>
+    <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
+    <hyperlink ref="H96" r:id="rId95"/>
+    <hyperlink ref="H97" r:id="rId96"/>
+    <hyperlink ref="H98" r:id="rId97"/>
+    <hyperlink ref="H99" r:id="rId98"/>
+    <hyperlink ref="H100" r:id="rId99"/>
+    <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
+    <hyperlink ref="H103" r:id="rId102"/>
+    <hyperlink ref="H104" r:id="rId103"/>
+    <hyperlink ref="H105" r:id="rId104"/>
+    <hyperlink ref="H106" r:id="rId105"/>
+    <hyperlink ref="H107" r:id="rId106"/>
+    <hyperlink ref="H108" r:id="rId107"/>
+    <hyperlink ref="H109" r:id="rId108"/>
+    <hyperlink ref="H110" r:id="rId109"/>
+    <hyperlink ref="H111" r:id="rId110"/>
+    <hyperlink ref="H112" r:id="rId111"/>
+    <hyperlink ref="H113" r:id="rId112"/>
+    <hyperlink ref="H114" r:id="rId113"/>
+    <hyperlink ref="H115" r:id="rId114"/>
+    <hyperlink ref="H116" r:id="rId115"/>
+    <hyperlink ref="H117" r:id="rId116"/>
+    <hyperlink ref="H118" r:id="rId117"/>
+    <hyperlink ref="H119" r:id="rId118"/>
+    <hyperlink ref="H120" r:id="rId119"/>
+    <hyperlink ref="H121" r:id="rId120"/>
+    <hyperlink ref="H122" r:id="rId121"/>
+    <hyperlink ref="H123" r:id="rId122"/>
+    <hyperlink ref="H124" r:id="rId123"/>
+    <hyperlink ref="H125" r:id="rId124"/>
+    <hyperlink ref="H126" r:id="rId125"/>
+    <hyperlink ref="H127" r:id="rId126"/>
+    <hyperlink ref="H128" r:id="rId127"/>
+    <hyperlink ref="H129" r:id="rId128"/>
+    <hyperlink ref="H130" r:id="rId129"/>
+    <hyperlink ref="H131" r:id="rId130"/>
+    <hyperlink ref="H132" r:id="rId131"/>
+    <hyperlink ref="H133" r:id="rId132"/>
+    <hyperlink ref="H134" r:id="rId133"/>
+    <hyperlink ref="H135" r:id="rId134"/>
+    <hyperlink ref="H136" r:id="rId135"/>
+    <hyperlink ref="H137" r:id="rId136"/>
+    <hyperlink ref="H138" r:id="rId137"/>
+    <hyperlink ref="H139" r:id="rId138"/>
+    <hyperlink ref="H140" r:id="rId139"/>
+    <hyperlink ref="H141" r:id="rId140"/>
+    <hyperlink ref="H142" r:id="rId141"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
